--- a/12602477.xlsx
+++ b/12602477.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -204,6 +204,15 @@
   </si>
   <si>
     <t>it was a boring day</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>Satisfied</t>
+  </si>
+  <si>
+    <t>it was a good day</t>
   </si>
 </sst>
 </file>
@@ -1016,26 +1025,50 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="11" t="str">
+      <c r="A7" s="8">
+        <v>46255</v>
+      </c>
+      <c r="B7" s="10">
+        <v>420</v>
+      </c>
+      <c r="C7" s="10">
+        <v>60</v>
+      </c>
+      <c r="D7" s="10">
+        <v>90</v>
+      </c>
+      <c r="E7" s="10">
+        <v>250</v>
+      </c>
+      <c r="F7" s="10">
+        <v>300</v>
+      </c>
+      <c r="G7" s="10">
+        <v>6</v>
+      </c>
+      <c r="H7" s="10">
+        <v>90</v>
+      </c>
+      <c r="I7" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="11" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J7" s="11">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="13"/>
+        <v>230</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="M7" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="N7" s="13" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>

--- a/12602477.xlsx
+++ b/12602477.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -213,6 +213,9 @@
   </si>
   <si>
     <t>it was a good day</t>
+  </si>
+  <si>
+    <t>High</t>
   </si>
 </sst>
 </file>
@@ -1071,26 +1074,50 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="11" t="str">
+      <c r="A8" s="8">
+        <v>46257</v>
+      </c>
+      <c r="B8" s="10">
+        <v>480</v>
+      </c>
+      <c r="C8" s="10">
+        <v>45</v>
+      </c>
+      <c r="D8" s="10">
+        <v>60</v>
+      </c>
+      <c r="E8" s="10">
+        <v>120</v>
+      </c>
+      <c r="F8" s="10">
+        <v>0</v>
+      </c>
+      <c r="G8" s="10">
+        <v>0</v>
+      </c>
+      <c r="H8" s="10">
+        <v>120</v>
+      </c>
+      <c r="I8" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="11" t="str">
+        <v>825</v>
+      </c>
+      <c r="J8" s="11">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
-      <c r="N8" s="13"/>
+        <v>615</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="L8" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="9"/>

--- a/12602477.xlsx
+++ b/12602477.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sweeti Oli\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Naman\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A659334F-6A31-4BA6-B142-6EC4009278E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9780" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -217,11 +218,32 @@
   <si>
     <t>High</t>
   </si>
+  <si>
+    <t>it was an okay day</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>it was  a holdiay, so it was a good day</t>
+  </si>
+  <si>
+    <t>it was an energetic day</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>it was a hectic day</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -661,7 +683,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A39"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -852,7 +874,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N400"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1120,161 +1142,331 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="11" t="str">
+      <c r="A9" s="8">
+        <v>46259</v>
+      </c>
+      <c r="B9" s="10">
+        <v>480</v>
+      </c>
+      <c r="C9" s="10">
+        <v>60</v>
+      </c>
+      <c r="D9" s="10">
+        <v>90</v>
+      </c>
+      <c r="E9" s="10">
+        <v>150</v>
+      </c>
+      <c r="F9" s="10">
+        <v>350</v>
+      </c>
+      <c r="G9" s="10">
+        <v>7</v>
+      </c>
+      <c r="H9" s="10">
+        <v>90</v>
+      </c>
+      <c r="I9" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="11" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J9" s="11">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
-      <c r="N9" s="13"/>
+        <v>220</v>
+      </c>
+      <c r="K9" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="L9" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="M9" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="11" t="str">
+      <c r="A10" s="8">
+        <v>46261</v>
+      </c>
+      <c r="B10" s="10">
+        <v>420</v>
+      </c>
+      <c r="C10" s="10">
+        <v>65</v>
+      </c>
+      <c r="D10" s="10">
+        <v>60</v>
+      </c>
+      <c r="E10" s="10">
+        <v>100</v>
+      </c>
+      <c r="F10" s="10">
+        <v>350</v>
+      </c>
+      <c r="G10" s="10">
+        <v>7</v>
+      </c>
+      <c r="H10" s="10">
+        <v>90</v>
+      </c>
+      <c r="I10" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="11" t="str">
+        <v>1085</v>
+      </c>
+      <c r="J10" s="11">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="13"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="9"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="11" t="str">
+        <v>355</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="L10" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="M10" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>46263</v>
+      </c>
+      <c r="B11" s="10">
+        <v>560</v>
+      </c>
+      <c r="C11" s="10">
+        <v>45</v>
+      </c>
+      <c r="D11" s="10">
+        <v>120</v>
+      </c>
+      <c r="E11" s="10">
+        <v>90</v>
+      </c>
+      <c r="F11" s="10">
+        <v>0</v>
+      </c>
+      <c r="G11" s="10">
+        <v>0</v>
+      </c>
+      <c r="H11" s="10">
+        <v>240</v>
+      </c>
+      <c r="I11" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="11" t="str">
+        <v>1055</v>
+      </c>
+      <c r="J11" s="11">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="13"/>
+        <v>385</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="M11" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="N11" s="13" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="11" t="str">
+      <c r="A12" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B12" s="10">
+        <v>420</v>
+      </c>
+      <c r="C12" s="10">
+        <v>60</v>
+      </c>
+      <c r="D12" s="10">
+        <v>60</v>
+      </c>
+      <c r="E12" s="10">
+        <v>120</v>
+      </c>
+      <c r="F12" s="10">
+        <v>150</v>
+      </c>
+      <c r="G12" s="10">
+        <v>3</v>
+      </c>
+      <c r="H12" s="10">
+        <v>160</v>
+      </c>
+      <c r="I12" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="11" t="str">
+        <v>970</v>
+      </c>
+      <c r="J12" s="11">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="13"/>
+        <v>470</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="M12" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="11" t="str">
+      <c r="A13" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B13" s="10">
+        <v>420</v>
+      </c>
+      <c r="C13" s="10">
+        <v>45</v>
+      </c>
+      <c r="D13" s="10">
+        <v>60</v>
+      </c>
+      <c r="E13" s="10">
+        <v>90</v>
+      </c>
+      <c r="F13" s="10">
+        <v>200</v>
+      </c>
+      <c r="G13" s="10">
+        <v>4</v>
+      </c>
+      <c r="H13" s="10">
+        <v>135</v>
+      </c>
+      <c r="I13" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="11" t="str">
+        <v>950</v>
+      </c>
+      <c r="J13" s="11">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="13"/>
+        <v>490</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="M13" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="11" t="str">
+      <c r="A14" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B14" s="10">
+        <v>480</v>
+      </c>
+      <c r="C14" s="10">
+        <v>45</v>
+      </c>
+      <c r="D14" s="10">
+        <v>120</v>
+      </c>
+      <c r="E14" s="10">
+        <v>90</v>
+      </c>
+      <c r="F14" s="10">
+        <v>300</v>
+      </c>
+      <c r="G14" s="10">
+        <v>6</v>
+      </c>
+      <c r="H14" s="10">
+        <v>100</v>
+      </c>
+      <c r="I14" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="11" t="str">
+        <v>1135</v>
+      </c>
+      <c r="J14" s="11">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="13"/>
+        <v>305</v>
+      </c>
+      <c r="K14" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="L14" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="M14" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="N14" s="13" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="9"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="11" t="str">
+      <c r="A15" s="8">
+        <v>46271</v>
+      </c>
+      <c r="B15" s="10">
+        <v>560</v>
+      </c>
+      <c r="C15" s="10">
+        <v>60</v>
+      </c>
+      <c r="D15" s="10">
+        <v>240</v>
+      </c>
+      <c r="E15" s="10">
+        <v>120</v>
+      </c>
+      <c r="F15" s="10">
+        <v>0</v>
+      </c>
+      <c r="G15" s="10">
+        <v>0</v>
+      </c>
+      <c r="H15" s="10">
+        <v>120</v>
+      </c>
+      <c r="I15" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="11" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J15" s="11">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="13"/>
+        <v>340</v>
+      </c>
+      <c r="K15" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="L15" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="M15" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="N15" s="13" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="9"/>
+      <c r="A16" s="8">
+        <v>46273</v>
+      </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
@@ -1296,7 +1488,9 @@
       <c r="N16" s="13"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="9"/>
+      <c r="A17" s="8">
+        <v>46275</v>
+      </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
@@ -1318,7 +1512,7 @@
       <c r="N17" s="13"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="9"/>
+      <c r="A18" s="8"/>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
@@ -1340,7 +1534,7 @@
       <c r="N18" s="13"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="9"/>
+      <c r="A19" s="8"/>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
@@ -9758,15 +9952,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K400">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K400" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L400">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L400" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M400">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M400" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12602477.xlsx
+++ b/12602477.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Naman\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A659334F-6A31-4BA6-B142-6EC4009278E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A900FCA2-1FC9-402F-99DC-ADB11167E749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -238,6 +238,12 @@
   </si>
   <si>
     <t>it was a hectic day</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>it was an amazing day</t>
   </si>
 </sst>
 </file>
@@ -1467,25 +1473,47 @@
       <c r="A16" s="8">
         <v>46273</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="11" t="str">
+      <c r="B16" s="10">
+        <v>480</v>
+      </c>
+      <c r="C16" s="10">
+        <v>60</v>
+      </c>
+      <c r="D16" s="10">
+        <v>60</v>
+      </c>
+      <c r="E16" s="10">
+        <v>90</v>
+      </c>
+      <c r="F16" s="10">
+        <v>350</v>
+      </c>
+      <c r="G16" s="10">
+        <v>7</v>
+      </c>
+      <c r="H16" s="10">
+        <v>120</v>
+      </c>
+      <c r="I16" s="11">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="11" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J16" s="11">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="12"/>
-      <c r="N16" s="13"/>
+        <v>280</v>
+      </c>
+      <c r="K16" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="M16" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="N16" s="13" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="8">

--- a/12602477.xlsx
+++ b/12602477.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sweeti Oli\OneDrive\Desktop\CAP776\12602477\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sweeti Oli\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -388,9 +388,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -406,6 +403,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -888,74 +888,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="19">
         <v>12602477</v>
       </c>
-      <c r="G2" s="14"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="14"/>
+      <c r="G3" s="19"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1002,548 +1002,548 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="15">
+      <c r="A6" s="12">
         <v>46253</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="13">
         <v>360</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="13">
         <v>60</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="13">
         <v>60</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="13">
         <v>150</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="13">
         <v>200</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="13">
         <v>4</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="13">
         <v>90</v>
       </c>
-      <c r="I6" s="17">
+      <c r="I6" s="14">
         <f t="shared" ref="I6:I68" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>920</v>
       </c>
-      <c r="J6" s="17">
+      <c r="J6" s="14">
         <v>520</v>
       </c>
-      <c r="K6" s="18" t="s">
+      <c r="K6" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="L6" s="18" t="s">
+      <c r="L6" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="M6" s="18" t="s">
+      <c r="M6" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="N6" s="19" t="s">
+      <c r="N6" s="16" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="15">
+      <c r="A7" s="12">
         <v>46255</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="13">
         <v>420</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="13">
         <v>60</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="13">
         <v>90</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="13">
         <v>250</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="13">
         <v>300</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="13">
         <v>6</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="13">
         <v>90</v>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="14">
         <f t="shared" si="0"/>
         <v>1210</v>
       </c>
-      <c r="J7" s="17">
+      <c r="J7" s="14">
         <v>230</v>
       </c>
-      <c r="K7" s="18" t="s">
+      <c r="K7" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="18" t="s">
+      <c r="L7" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="M7" s="18" t="s">
+      <c r="M7" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="N7" s="19" t="s">
+      <c r="N7" s="16" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="15">
+      <c r="A8" s="12">
         <v>46257</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="13">
         <v>480</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="13">
         <v>45</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="13">
         <v>60</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="13">
         <v>120</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="13">
         <v>0</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="13">
         <v>0</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="13">
         <v>120</v>
       </c>
-      <c r="I8" s="17">
+      <c r="I8" s="14">
         <f t="shared" si="0"/>
         <v>825</v>
       </c>
-      <c r="J8" s="17">
+      <c r="J8" s="14">
         <v>615</v>
       </c>
-      <c r="K8" s="18" t="s">
+      <c r="K8" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="L8" s="18" t="s">
+      <c r="L8" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="M8" s="18" t="s">
+      <c r="M8" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="N8" s="19" t="s">
+      <c r="N8" s="16" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="15">
+      <c r="A9" s="12">
         <v>46259</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="13">
         <v>480</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="13">
         <v>60</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="13">
         <v>90</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="13">
         <v>150</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="13">
         <v>350</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="13">
         <v>7</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="13">
         <v>90</v>
       </c>
-      <c r="I9" s="17">
+      <c r="I9" s="14">
         <f t="shared" si="0"/>
         <v>1220</v>
       </c>
-      <c r="J9" s="17">
+      <c r="J9" s="14">
         <v>220</v>
       </c>
-      <c r="K9" s="18" t="s">
+      <c r="K9" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="L9" s="18" t="s">
+      <c r="L9" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="M9" s="18" t="s">
+      <c r="M9" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="N9" s="19" t="s">
+      <c r="N9" s="16" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="15">
+      <c r="A10" s="12">
         <v>46261</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="13">
         <v>420</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="13">
         <v>65</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="13">
         <v>60</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="13">
         <v>100</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="13">
         <v>350</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="13">
         <v>7</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="13">
         <v>90</v>
       </c>
-      <c r="I10" s="17">
+      <c r="I10" s="14">
         <f t="shared" si="0"/>
         <v>1085</v>
       </c>
-      <c r="J10" s="17">
+      <c r="J10" s="14">
         <v>355</v>
       </c>
-      <c r="K10" s="18" t="s">
+      <c r="K10" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="18" t="s">
+      <c r="L10" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="M10" s="18" t="s">
+      <c r="M10" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="N10" s="19" t="s">
+      <c r="N10" s="16" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="15">
+      <c r="A11" s="12">
         <v>46263</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="13">
         <v>560</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="13">
         <v>45</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="13">
         <v>120</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="13">
         <v>90</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="13">
         <v>0</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="13">
         <v>0</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="13">
         <v>240</v>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="14">
         <f t="shared" si="0"/>
         <v>1055</v>
       </c>
-      <c r="J11" s="17">
+      <c r="J11" s="14">
         <v>385</v>
       </c>
-      <c r="K11" s="18" t="s">
+      <c r="K11" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="L11" s="18" t="s">
+      <c r="L11" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="M11" s="18" t="s">
+      <c r="M11" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="N11" s="19" t="s">
+      <c r="N11" s="16" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="15">
+      <c r="A12" s="12">
         <v>46265</v>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="13">
         <v>420</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="13">
         <v>60</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="13">
         <v>60</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="13">
         <v>120</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="13">
         <v>150</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="13">
         <v>3</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="13">
         <v>160</v>
       </c>
-      <c r="I12" s="17">
+      <c r="I12" s="14">
         <f t="shared" si="0"/>
         <v>970</v>
       </c>
-      <c r="J12" s="17">
+      <c r="J12" s="14">
         <v>470</v>
       </c>
-      <c r="K12" s="18" t="s">
+      <c r="K12" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="L12" s="18" t="s">
+      <c r="L12" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="M12" s="18" t="s">
+      <c r="M12" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="N12" s="19" t="s">
+      <c r="N12" s="16" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="15">
+      <c r="A13" s="12">
         <v>46267</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="13">
         <v>420</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="13">
         <v>45</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="13">
         <v>60</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="13">
         <v>90</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="13">
         <v>200</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="13">
         <v>4</v>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="13">
         <v>135</v>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="14">
         <f t="shared" si="0"/>
         <v>950</v>
       </c>
-      <c r="J13" s="17">
+      <c r="J13" s="14">
         <v>490</v>
       </c>
-      <c r="K13" s="18" t="s">
+      <c r="K13" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="L13" s="18" t="s">
+      <c r="L13" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="M13" s="18" t="s">
+      <c r="M13" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="N13" s="19" t="s">
+      <c r="N13" s="16" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="15">
+      <c r="A14" s="12">
         <v>46269</v>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="13">
         <v>480</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="13">
         <v>45</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="13">
         <v>120</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="13">
         <v>90</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="13">
         <v>300</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="13">
         <v>6</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="13">
         <v>100</v>
       </c>
-      <c r="I14" s="17">
+      <c r="I14" s="14">
         <f t="shared" si="0"/>
         <v>1135</v>
       </c>
-      <c r="J14" s="17">
+      <c r="J14" s="14">
         <v>305</v>
       </c>
-      <c r="K14" s="18" t="s">
+      <c r="K14" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="L14" s="18" t="s">
+      <c r="L14" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="M14" s="18" t="s">
+      <c r="M14" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N14" s="19" t="s">
+      <c r="N14" s="16" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="15">
+      <c r="A15" s="12">
         <v>46271</v>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="13">
         <v>560</v>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="13">
         <v>60</v>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="13">
         <v>240</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="13">
         <v>120</v>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="13">
         <v>0</v>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="13">
         <v>0</v>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="13">
         <v>120</v>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="14">
         <f t="shared" si="0"/>
         <v>1100</v>
       </c>
-      <c r="J15" s="17">
+      <c r="J15" s="14">
         <v>340</v>
       </c>
-      <c r="K15" s="18" t="s">
+      <c r="K15" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="L15" s="18" t="s">
+      <c r="L15" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="M15" s="18" t="s">
+      <c r="M15" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="N15" s="19" t="s">
+      <c r="N15" s="16" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="15">
+      <c r="A16" s="12">
         <v>46273</v>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="13">
         <v>480</v>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="13">
         <v>60</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="13">
         <v>60</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="13">
         <v>90</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="13">
         <v>350</v>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="13">
         <v>7</v>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="13">
         <v>120</v>
       </c>
-      <c r="I16" s="17">
+      <c r="I16" s="14">
         <f t="shared" si="0"/>
         <v>1160</v>
       </c>
-      <c r="J16" s="17">
+      <c r="J16" s="14">
         <v>280</v>
       </c>
-      <c r="K16" s="18" t="s">
+      <c r="K16" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="L16" s="18" t="s">
+      <c r="L16" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="M16" s="18" t="s">
+      <c r="M16" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="N16" s="19" t="s">
+      <c r="N16" s="16" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="15">
+      <c r="A17" s="12">
         <v>46275</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="13">
         <v>480</v>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="13">
         <v>60</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="13">
         <v>120</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="13">
         <v>60</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="13">
         <v>350</v>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="13">
         <v>7</v>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="13">
         <v>90</v>
       </c>
-      <c r="I17" s="17">
+      <c r="I17" s="14">
         <f t="shared" si="0"/>
         <v>1160</v>
       </c>
-      <c r="J17" s="17">
+      <c r="J17" s="14">
         <f>IF(I17="","",1440-I17)</f>
         <v>280</v>
       </c>
-      <c r="K17" s="18" t="s">
+      <c r="K17" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="L17" s="18" t="s">
+      <c r="L17" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="M17" s="18" t="s">
+      <c r="M17" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="N17" s="19" t="s">
+      <c r="N17" s="16" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="15">
+      <c r="A18" s="12">
         <v>46277</v>
       </c>
       <c r="B18" s="8">
@@ -1567,12 +1567,12 @@
       <c r="H18" s="8">
         <v>240</v>
       </c>
-      <c r="I18" s="17">
+      <c r="I18" s="14">
         <f t="shared" si="0"/>
         <v>1055</v>
       </c>
       <c r="J18" s="9">
-        <f t="shared" ref="J6:J68" si="1">IF(I18="","",1440-I18)</f>
+        <f t="shared" ref="J18:J68" si="1">IF(I18="","",1440-I18)</f>
         <v>385</v>
       </c>
       <c r="K18" s="10" t="s">
@@ -1584,12 +1584,12 @@
       <c r="M18" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="N18" s="19" t="s">
+      <c r="N18" s="16" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="15">
+      <c r="A19" s="12">
         <v>46279</v>
       </c>
       <c r="B19" s="8">
@@ -1613,11 +1613,11 @@
       <c r="H19" s="8">
         <v>240</v>
       </c>
-      <c r="I19" s="17">
+      <c r="I19" s="14">
         <f t="shared" si="0"/>
         <v>1080</v>
       </c>
-      <c r="J19" s="17">
+      <c r="J19" s="14">
         <f t="shared" si="1"/>
         <v>360</v>
       </c>
@@ -1635,31 +1635,53 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="15">
+      <c r="A20" s="12">
         <v>46281</v>
       </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="9" t="str">
+      <c r="B20" s="8">
+        <v>560</v>
+      </c>
+      <c r="C20" s="8">
+        <v>45</v>
+      </c>
+      <c r="D20" s="8">
+        <v>120</v>
+      </c>
+      <c r="E20" s="8">
+        <v>60</v>
+      </c>
+      <c r="F20" s="8">
+        <v>0</v>
+      </c>
+      <c r="G20" s="8">
+        <v>0</v>
+      </c>
+      <c r="H20" s="8">
+        <v>240</v>
+      </c>
+      <c r="I20" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="9" t="str">
+        <v>1025</v>
+      </c>
+      <c r="J20" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="11"/>
+        <v>415</v>
+      </c>
+      <c r="K20" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L20" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="M20" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="N20" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="15">
+      <c r="A21" s="12">
         <v>46283</v>
       </c>
       <c r="B21" s="8"/>
@@ -1683,7 +1705,7 @@
       <c r="N21" s="11"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="15"/>
+      <c r="A22" s="12"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
@@ -1705,7 +1727,7 @@
       <c r="N22" s="11"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="15"/>
+      <c r="A23" s="12"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -1727,7 +1749,7 @@
       <c r="N23" s="11"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="15"/>
+      <c r="A24" s="12"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
@@ -1749,7 +1771,7 @@
       <c r="N24" s="11"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="15"/>
+      <c r="A25" s="12"/>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
@@ -1771,7 +1793,7 @@
       <c r="N25" s="11"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="15"/>
+      <c r="A26" s="12"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
@@ -1793,7 +1815,7 @@
       <c r="N26" s="11"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="15"/>
+      <c r="A27" s="12"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
@@ -1815,7 +1837,7 @@
       <c r="N27" s="11"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="15"/>
+      <c r="A28" s="12"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
@@ -1837,7 +1859,7 @@
       <c r="N28" s="11"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="15"/>
+      <c r="A29" s="12"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
@@ -1859,7 +1881,7 @@
       <c r="N29" s="11"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="15"/>
+      <c r="A30" s="12"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -1881,7 +1903,7 @@
       <c r="N30" s="11"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="15"/>
+      <c r="A31" s="12"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -1903,7 +1925,7 @@
       <c r="N31" s="11"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="15"/>
+      <c r="A32" s="12"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -1925,7 +1947,7 @@
       <c r="N32" s="11"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="15"/>
+      <c r="A33" s="12"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -1947,7 +1969,7 @@
       <c r="N33" s="11"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="15"/>
+      <c r="A34" s="12"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
@@ -1969,7 +1991,7 @@
       <c r="N34" s="11"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="15"/>
+      <c r="A35" s="12"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
@@ -1991,7 +2013,7 @@
       <c r="N35" s="11"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="15"/>
+      <c r="A36" s="12"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
@@ -2013,7 +2035,7 @@
       <c r="N36" s="11"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="15"/>
+      <c r="A37" s="12"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
@@ -2035,7 +2057,7 @@
       <c r="N37" s="11"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="15"/>
+      <c r="A38" s="12"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
@@ -2057,7 +2079,7 @@
       <c r="N38" s="11"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="15"/>
+      <c r="A39" s="12"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
@@ -2079,7 +2101,7 @@
       <c r="N39" s="11"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="15"/>
+      <c r="A40" s="12"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
@@ -2101,7 +2123,7 @@
       <c r="N40" s="11"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="15"/>
+      <c r="A41" s="12"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
@@ -2123,7 +2145,7 @@
       <c r="N41" s="11"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="15"/>
+      <c r="A42" s="12"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
@@ -2145,7 +2167,7 @@
       <c r="N42" s="11"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="15"/>
+      <c r="A43" s="12"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
@@ -2167,7 +2189,7 @@
       <c r="N43" s="11"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="15"/>
+      <c r="A44" s="12"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
@@ -2189,7 +2211,7 @@
       <c r="N44" s="11"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="15"/>
+      <c r="A45" s="12"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
       <c r="D45" s="8"/>
@@ -2211,7 +2233,7 @@
       <c r="N45" s="11"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="15"/>
+      <c r="A46" s="12"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
@@ -2233,7 +2255,7 @@
       <c r="N46" s="11"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="15"/>
+      <c r="A47" s="12"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
@@ -2255,7 +2277,7 @@
       <c r="N47" s="11"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="15"/>
+      <c r="A48" s="12"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
@@ -2277,7 +2299,7 @@
       <c r="N48" s="11"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="15"/>
+      <c r="A49" s="12"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
@@ -2299,7 +2321,7 @@
       <c r="N49" s="11"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="15"/>
+      <c r="A50" s="12"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
@@ -2321,7 +2343,7 @@
       <c r="N50" s="11"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="15"/>
+      <c r="A51" s="12"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
@@ -2343,7 +2365,7 @@
       <c r="N51" s="11"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="15"/>
+      <c r="A52" s="12"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
@@ -2365,7 +2387,7 @@
       <c r="N52" s="11"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="15"/>
+      <c r="A53" s="12"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
@@ -2387,7 +2409,7 @@
       <c r="N53" s="11"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="15"/>
+      <c r="A54" s="12"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
@@ -2409,7 +2431,7 @@
       <c r="N54" s="11"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="15"/>
+      <c r="A55" s="12"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
@@ -2431,7 +2453,7 @@
       <c r="N55" s="11"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="15"/>
+      <c r="A56" s="12"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
       <c r="D56" s="8"/>
@@ -2453,7 +2475,7 @@
       <c r="N56" s="11"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="15"/>
+      <c r="A57" s="12"/>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
       <c r="D57" s="8"/>
@@ -2475,7 +2497,7 @@
       <c r="N57" s="11"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="15"/>
+      <c r="A58" s="12"/>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
       <c r="D58" s="8"/>
@@ -2497,7 +2519,7 @@
       <c r="N58" s="11"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="15"/>
+      <c r="A59" s="12"/>
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
@@ -2519,7 +2541,7 @@
       <c r="N59" s="11"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="15"/>
+      <c r="A60" s="12"/>
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
       <c r="D60" s="8"/>
@@ -2541,7 +2563,7 @@
       <c r="N60" s="11"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="15"/>
+      <c r="A61" s="12"/>
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
@@ -2563,7 +2585,7 @@
       <c r="N61" s="11"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="15"/>
+      <c r="A62" s="12"/>
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
       <c r="D62" s="8"/>
@@ -2585,7 +2607,7 @@
       <c r="N62" s="11"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="15"/>
+      <c r="A63" s="12"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
       <c r="D63" s="8"/>
@@ -2607,7 +2629,7 @@
       <c r="N63" s="11"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="15"/>
+      <c r="A64" s="12"/>
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
       <c r="D64" s="8"/>
@@ -2629,7 +2651,7 @@
       <c r="N64" s="11"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="15"/>
+      <c r="A65" s="12"/>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
       <c r="D65" s="8"/>
@@ -2651,7 +2673,7 @@
       <c r="N65" s="11"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="15"/>
+      <c r="A66" s="12"/>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
       <c r="D66" s="8"/>
@@ -2673,7 +2695,7 @@
       <c r="N66" s="11"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="15"/>
+      <c r="A67" s="12"/>
       <c r="B67" s="8"/>
       <c r="C67" s="8"/>
       <c r="D67" s="8"/>
@@ -2695,7 +2717,7 @@
       <c r="N67" s="11"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="15"/>
+      <c r="A68" s="12"/>
       <c r="B68" s="8"/>
       <c r="C68" s="8"/>
       <c r="D68" s="8"/>
@@ -2717,7 +2739,7 @@
       <c r="N68" s="11"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="15"/>
+      <c r="A69" s="12"/>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
       <c r="D69" s="8"/>
@@ -2739,7 +2761,7 @@
       <c r="N69" s="11"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="15"/>
+      <c r="A70" s="12"/>
       <c r="B70" s="8"/>
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
@@ -2761,7 +2783,7 @@
       <c r="N70" s="11"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="15"/>
+      <c r="A71" s="12"/>
       <c r="B71" s="8"/>
       <c r="C71" s="8"/>
       <c r="D71" s="8"/>
@@ -2783,7 +2805,7 @@
       <c r="N71" s="11"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="15"/>
+      <c r="A72" s="12"/>
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
       <c r="D72" s="8"/>
@@ -2805,7 +2827,7 @@
       <c r="N72" s="11"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="15"/>
+      <c r="A73" s="12"/>
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
       <c r="D73" s="8"/>
@@ -2827,7 +2849,7 @@
       <c r="N73" s="11"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="15"/>
+      <c r="A74" s="12"/>
       <c r="B74" s="8"/>
       <c r="C74" s="8"/>
       <c r="D74" s="8"/>
@@ -2849,7 +2871,7 @@
       <c r="N74" s="11"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="15"/>
+      <c r="A75" s="12"/>
       <c r="B75" s="8"/>
       <c r="C75" s="8"/>
       <c r="D75" s="8"/>
@@ -2871,7 +2893,7 @@
       <c r="N75" s="11"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" s="15"/>
+      <c r="A76" s="12"/>
       <c r="B76" s="8"/>
       <c r="C76" s="8"/>
       <c r="D76" s="8"/>
@@ -2893,7 +2915,7 @@
       <c r="N76" s="11"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="15"/>
+      <c r="A77" s="12"/>
       <c r="B77" s="8"/>
       <c r="C77" s="8"/>
       <c r="D77" s="8"/>
@@ -2915,7 +2937,7 @@
       <c r="N77" s="11"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" s="15"/>
+      <c r="A78" s="12"/>
       <c r="B78" s="8"/>
       <c r="C78" s="8"/>
       <c r="D78" s="8"/>
@@ -2937,7 +2959,7 @@
       <c r="N78" s="11"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A79" s="15"/>
+      <c r="A79" s="12"/>
       <c r="B79" s="8"/>
       <c r="C79" s="8"/>
       <c r="D79" s="8"/>
@@ -2959,7 +2981,7 @@
       <c r="N79" s="11"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A80" s="15"/>
+      <c r="A80" s="12"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
       <c r="D80" s="8"/>
@@ -2981,7 +3003,7 @@
       <c r="N80" s="11"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A81" s="15"/>
+      <c r="A81" s="12"/>
       <c r="B81" s="8"/>
       <c r="C81" s="8"/>
       <c r="D81" s="8"/>
@@ -3003,7 +3025,7 @@
       <c r="N81" s="11"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A82" s="15"/>
+      <c r="A82" s="12"/>
       <c r="B82" s="8"/>
       <c r="C82" s="8"/>
       <c r="D82" s="8"/>
@@ -3025,7 +3047,7 @@
       <c r="N82" s="11"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A83" s="15"/>
+      <c r="A83" s="12"/>
       <c r="B83" s="8"/>
       <c r="C83" s="8"/>
       <c r="D83" s="8"/>
@@ -3047,7 +3069,7 @@
       <c r="N83" s="11"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A84" s="15"/>
+      <c r="A84" s="12"/>
       <c r="B84" s="8"/>
       <c r="C84" s="8"/>
       <c r="D84" s="8"/>
@@ -3069,7 +3091,7 @@
       <c r="N84" s="11"/>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A85" s="15"/>
+      <c r="A85" s="12"/>
       <c r="B85" s="8"/>
       <c r="C85" s="8"/>
       <c r="D85" s="8"/>
@@ -3091,7 +3113,7 @@
       <c r="N85" s="11"/>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A86" s="15"/>
+      <c r="A86" s="12"/>
       <c r="B86" s="8"/>
       <c r="C86" s="8"/>
       <c r="D86" s="8"/>
@@ -3113,7 +3135,7 @@
       <c r="N86" s="11"/>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A87" s="15"/>
+      <c r="A87" s="12"/>
       <c r="B87" s="8"/>
       <c r="C87" s="8"/>
       <c r="D87" s="8"/>
@@ -3135,7 +3157,7 @@
       <c r="N87" s="11"/>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A88" s="15"/>
+      <c r="A88" s="12"/>
       <c r="B88" s="8"/>
       <c r="C88" s="8"/>
       <c r="D88" s="8"/>
@@ -3157,7 +3179,7 @@
       <c r="N88" s="11"/>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A89" s="15"/>
+      <c r="A89" s="12"/>
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
       <c r="D89" s="8"/>
@@ -3179,7 +3201,7 @@
       <c r="N89" s="11"/>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A90" s="15"/>
+      <c r="A90" s="12"/>
       <c r="B90" s="8"/>
       <c r="C90" s="8"/>
       <c r="D90" s="8"/>
@@ -3201,7 +3223,7 @@
       <c r="N90" s="11"/>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A91" s="15"/>
+      <c r="A91" s="12"/>
       <c r="B91" s="8"/>
       <c r="C91" s="8"/>
       <c r="D91" s="8"/>
@@ -3223,7 +3245,7 @@
       <c r="N91" s="11"/>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A92" s="15"/>
+      <c r="A92" s="12"/>
       <c r="B92" s="8"/>
       <c r="C92" s="8"/>
       <c r="D92" s="8"/>
@@ -3245,7 +3267,7 @@
       <c r="N92" s="11"/>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A93" s="15"/>
+      <c r="A93" s="12"/>
       <c r="B93" s="8"/>
       <c r="C93" s="8"/>
       <c r="D93" s="8"/>
@@ -3267,7 +3289,7 @@
       <c r="N93" s="11"/>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A94" s="15"/>
+      <c r="A94" s="12"/>
       <c r="B94" s="8"/>
       <c r="C94" s="8"/>
       <c r="D94" s="8"/>
@@ -3289,7 +3311,7 @@
       <c r="N94" s="11"/>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A95" s="15"/>
+      <c r="A95" s="12"/>
       <c r="B95" s="8"/>
       <c r="C95" s="8"/>
       <c r="D95" s="8"/>
@@ -3311,7 +3333,7 @@
       <c r="N95" s="11"/>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A96" s="15"/>
+      <c r="A96" s="12"/>
       <c r="B96" s="8"/>
       <c r="C96" s="8"/>
       <c r="D96" s="8"/>
@@ -3333,7 +3355,7 @@
       <c r="N96" s="11"/>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A97" s="15"/>
+      <c r="A97" s="12"/>
       <c r="B97" s="8"/>
       <c r="C97" s="8"/>
       <c r="D97" s="8"/>
@@ -3355,7 +3377,7 @@
       <c r="N97" s="11"/>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A98" s="15"/>
+      <c r="A98" s="12"/>
       <c r="B98" s="8"/>
       <c r="C98" s="8"/>
       <c r="D98" s="8"/>
@@ -3377,7 +3399,7 @@
       <c r="N98" s="11"/>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A99" s="15"/>
+      <c r="A99" s="12"/>
       <c r="B99" s="8"/>
       <c r="C99" s="8"/>
       <c r="D99" s="8"/>
@@ -3399,7 +3421,7 @@
       <c r="N99" s="11"/>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A100" s="15"/>
+      <c r="A100" s="12"/>
       <c r="B100" s="8"/>
       <c r="C100" s="8"/>
       <c r="D100" s="8"/>
@@ -3421,7 +3443,7 @@
       <c r="N100" s="11"/>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A101" s="15"/>
+      <c r="A101" s="12"/>
       <c r="B101" s="8"/>
       <c r="C101" s="8"/>
       <c r="D101" s="8"/>
@@ -3443,7 +3465,7 @@
       <c r="N101" s="11"/>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A102" s="15"/>
+      <c r="A102" s="12"/>
       <c r="B102" s="8"/>
       <c r="C102" s="8"/>
       <c r="D102" s="8"/>
@@ -3465,7 +3487,7 @@
       <c r="N102" s="11"/>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A103" s="15"/>
+      <c r="A103" s="12"/>
       <c r="B103" s="8"/>
       <c r="C103" s="8"/>
       <c r="D103" s="8"/>
@@ -3487,7 +3509,7 @@
       <c r="N103" s="11"/>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A104" s="15"/>
+      <c r="A104" s="12"/>
       <c r="B104" s="8"/>
       <c r="C104" s="8"/>
       <c r="D104" s="8"/>
@@ -3509,7 +3531,7 @@
       <c r="N104" s="11"/>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A105" s="15"/>
+      <c r="A105" s="12"/>
       <c r="B105" s="8"/>
       <c r="C105" s="8"/>
       <c r="D105" s="8"/>
@@ -3531,7 +3553,7 @@
       <c r="N105" s="11"/>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A106" s="15"/>
+      <c r="A106" s="12"/>
       <c r="B106" s="8"/>
       <c r="C106" s="8"/>
       <c r="D106" s="8"/>
@@ -3553,7 +3575,7 @@
       <c r="N106" s="11"/>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A107" s="15"/>
+      <c r="A107" s="12"/>
       <c r="B107" s="8"/>
       <c r="C107" s="8"/>
       <c r="D107" s="8"/>
@@ -3575,7 +3597,7 @@
       <c r="N107" s="11"/>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A108" s="15"/>
+      <c r="A108" s="12"/>
       <c r="B108" s="8"/>
       <c r="C108" s="8"/>
       <c r="D108" s="8"/>
@@ -3597,7 +3619,7 @@
       <c r="N108" s="11"/>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A109" s="15"/>
+      <c r="A109" s="12"/>
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
       <c r="D109" s="8"/>
@@ -3619,7 +3641,7 @@
       <c r="N109" s="11"/>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A110" s="15"/>
+      <c r="A110" s="12"/>
       <c r="B110" s="8"/>
       <c r="C110" s="8"/>
       <c r="D110" s="8"/>
@@ -3641,7 +3663,7 @@
       <c r="N110" s="11"/>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A111" s="15"/>
+      <c r="A111" s="12"/>
       <c r="B111" s="8"/>
       <c r="C111" s="8"/>
       <c r="D111" s="8"/>
@@ -3663,7 +3685,7 @@
       <c r="N111" s="11"/>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A112" s="15"/>
+      <c r="A112" s="12"/>
       <c r="B112" s="8"/>
       <c r="C112" s="8"/>
       <c r="D112" s="8"/>
@@ -3685,7 +3707,7 @@
       <c r="N112" s="11"/>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A113" s="15"/>
+      <c r="A113" s="12"/>
       <c r="B113" s="8"/>
       <c r="C113" s="8"/>
       <c r="D113" s="8"/>
@@ -3707,7 +3729,7 @@
       <c r="N113" s="11"/>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A114" s="15"/>
+      <c r="A114" s="12"/>
       <c r="B114" s="8"/>
       <c r="C114" s="8"/>
       <c r="D114" s="8"/>
@@ -3729,7 +3751,7 @@
       <c r="N114" s="11"/>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A115" s="15"/>
+      <c r="A115" s="12"/>
       <c r="B115" s="8"/>
       <c r="C115" s="8"/>
       <c r="D115" s="8"/>
@@ -3751,7 +3773,7 @@
       <c r="N115" s="11"/>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A116" s="15"/>
+      <c r="A116" s="12"/>
       <c r="B116" s="8"/>
       <c r="C116" s="8"/>
       <c r="D116" s="8"/>
@@ -3773,7 +3795,7 @@
       <c r="N116" s="11"/>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A117" s="15"/>
+      <c r="A117" s="12"/>
       <c r="B117" s="8"/>
       <c r="C117" s="8"/>
       <c r="D117" s="8"/>
@@ -3795,7 +3817,7 @@
       <c r="N117" s="11"/>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A118" s="15"/>
+      <c r="A118" s="12"/>
       <c r="B118" s="8"/>
       <c r="C118" s="8"/>
       <c r="D118" s="8"/>
@@ -3817,7 +3839,7 @@
       <c r="N118" s="11"/>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A119" s="15"/>
+      <c r="A119" s="12"/>
       <c r="B119" s="8"/>
       <c r="C119" s="8"/>
       <c r="D119" s="8"/>
@@ -3839,7 +3861,7 @@
       <c r="N119" s="11"/>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A120" s="15"/>
+      <c r="A120" s="12"/>
       <c r="B120" s="8"/>
       <c r="C120" s="8"/>
       <c r="D120" s="8"/>
@@ -3861,7 +3883,7 @@
       <c r="N120" s="11"/>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A121" s="15"/>
+      <c r="A121" s="12"/>
       <c r="B121" s="8"/>
       <c r="C121" s="8"/>
       <c r="D121" s="8"/>
@@ -3883,7 +3905,7 @@
       <c r="N121" s="11"/>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A122" s="15"/>
+      <c r="A122" s="12"/>
       <c r="B122" s="8"/>
       <c r="C122" s="8"/>
       <c r="D122" s="8"/>
@@ -3905,7 +3927,7 @@
       <c r="N122" s="11"/>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A123" s="15"/>
+      <c r="A123" s="12"/>
       <c r="B123" s="8"/>
       <c r="C123" s="8"/>
       <c r="D123" s="8"/>
@@ -3927,7 +3949,7 @@
       <c r="N123" s="11"/>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A124" s="15"/>
+      <c r="A124" s="12"/>
       <c r="B124" s="8"/>
       <c r="C124" s="8"/>
       <c r="D124" s="8"/>
@@ -3949,7 +3971,7 @@
       <c r="N124" s="11"/>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A125" s="15"/>
+      <c r="A125" s="12"/>
       <c r="B125" s="8"/>
       <c r="C125" s="8"/>
       <c r="D125" s="8"/>
@@ -3971,7 +3993,7 @@
       <c r="N125" s="11"/>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A126" s="15"/>
+      <c r="A126" s="12"/>
       <c r="B126" s="8"/>
       <c r="C126" s="8"/>
       <c r="D126" s="8"/>
@@ -3993,7 +4015,7 @@
       <c r="N126" s="11"/>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A127" s="15"/>
+      <c r="A127" s="12"/>
       <c r="B127" s="8"/>
       <c r="C127" s="8"/>
       <c r="D127" s="8"/>
@@ -4015,7 +4037,7 @@
       <c r="N127" s="11"/>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A128" s="15"/>
+      <c r="A128" s="12"/>
       <c r="B128" s="8"/>
       <c r="C128" s="8"/>
       <c r="D128" s="8"/>
@@ -4037,7 +4059,7 @@
       <c r="N128" s="11"/>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A129" s="15"/>
+      <c r="A129" s="12"/>
       <c r="B129" s="8"/>
       <c r="C129" s="8"/>
       <c r="D129" s="8"/>
@@ -4059,7 +4081,7 @@
       <c r="N129" s="11"/>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A130" s="15"/>
+      <c r="A130" s="12"/>
       <c r="B130" s="8"/>
       <c r="C130" s="8"/>
       <c r="D130" s="8"/>
@@ -4081,7 +4103,7 @@
       <c r="N130" s="11"/>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A131" s="15"/>
+      <c r="A131" s="12"/>
       <c r="B131" s="8"/>
       <c r="C131" s="8"/>
       <c r="D131" s="8"/>
@@ -4103,7 +4125,7 @@
       <c r="N131" s="11"/>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A132" s="15"/>
+      <c r="A132" s="12"/>
       <c r="B132" s="8"/>
       <c r="C132" s="8"/>
       <c r="D132" s="8"/>
@@ -4125,7 +4147,7 @@
       <c r="N132" s="11"/>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A133" s="15"/>
+      <c r="A133" s="12"/>
       <c r="B133" s="8"/>
       <c r="C133" s="8"/>
       <c r="D133" s="8"/>
@@ -4147,7 +4169,7 @@
       <c r="N133" s="11"/>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A134" s="15"/>
+      <c r="A134" s="12"/>
       <c r="B134" s="8"/>
       <c r="C134" s="8"/>
       <c r="D134" s="8"/>
@@ -4169,7 +4191,7 @@
       <c r="N134" s="11"/>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A135" s="15"/>
+      <c r="A135" s="12"/>
       <c r="B135" s="8"/>
       <c r="C135" s="8"/>
       <c r="D135" s="8"/>
@@ -4191,7 +4213,7 @@
       <c r="N135" s="11"/>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A136" s="15"/>
+      <c r="A136" s="12"/>
       <c r="B136" s="8"/>
       <c r="C136" s="8"/>
       <c r="D136" s="8"/>
@@ -4213,7 +4235,7 @@
       <c r="N136" s="11"/>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A137" s="15"/>
+      <c r="A137" s="12"/>
       <c r="B137" s="8"/>
       <c r="C137" s="8"/>
       <c r="D137" s="8"/>
@@ -4235,7 +4257,7 @@
       <c r="N137" s="11"/>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A138" s="15"/>
+      <c r="A138" s="12"/>
       <c r="B138" s="8"/>
       <c r="C138" s="8"/>
       <c r="D138" s="8"/>
@@ -4257,7 +4279,7 @@
       <c r="N138" s="11"/>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A139" s="15"/>
+      <c r="A139" s="12"/>
       <c r="B139" s="8"/>
       <c r="C139" s="8"/>
       <c r="D139" s="8"/>
@@ -4279,7 +4301,7 @@
       <c r="N139" s="11"/>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A140" s="15"/>
+      <c r="A140" s="12"/>
       <c r="B140" s="8"/>
       <c r="C140" s="8"/>
       <c r="D140" s="8"/>
@@ -4301,7 +4323,7 @@
       <c r="N140" s="11"/>
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A141" s="15"/>
+      <c r="A141" s="12"/>
       <c r="B141" s="8"/>
       <c r="C141" s="8"/>
       <c r="D141" s="8"/>
@@ -4323,7 +4345,7 @@
       <c r="N141" s="11"/>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A142" s="15"/>
+      <c r="A142" s="12"/>
       <c r="B142" s="8"/>
       <c r="C142" s="8"/>
       <c r="D142" s="8"/>
@@ -4345,7 +4367,7 @@
       <c r="N142" s="11"/>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A143" s="15"/>
+      <c r="A143" s="12"/>
       <c r="B143" s="8"/>
       <c r="C143" s="8"/>
       <c r="D143" s="8"/>
@@ -4367,7 +4389,7 @@
       <c r="N143" s="11"/>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A144" s="15"/>
+      <c r="A144" s="12"/>
       <c r="B144" s="8"/>
       <c r="C144" s="8"/>
       <c r="D144" s="8"/>
@@ -4389,7 +4411,7 @@
       <c r="N144" s="11"/>
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A145" s="15"/>
+      <c r="A145" s="12"/>
       <c r="B145" s="8"/>
       <c r="C145" s="8"/>
       <c r="D145" s="8"/>
@@ -4411,7 +4433,7 @@
       <c r="N145" s="11"/>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A146" s="15"/>
+      <c r="A146" s="12"/>
       <c r="B146" s="8"/>
       <c r="C146" s="8"/>
       <c r="D146" s="8"/>
@@ -4433,7 +4455,7 @@
       <c r="N146" s="11"/>
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A147" s="15"/>
+      <c r="A147" s="12"/>
       <c r="B147" s="8"/>
       <c r="C147" s="8"/>
       <c r="D147" s="8"/>
@@ -4455,7 +4477,7 @@
       <c r="N147" s="11"/>
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A148" s="15"/>
+      <c r="A148" s="12"/>
       <c r="B148" s="8"/>
       <c r="C148" s="8"/>
       <c r="D148" s="8"/>
@@ -4477,7 +4499,7 @@
       <c r="N148" s="11"/>
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A149" s="15"/>
+      <c r="A149" s="12"/>
       <c r="B149" s="8"/>
       <c r="C149" s="8"/>
       <c r="D149" s="8"/>
@@ -4499,7 +4521,7 @@
       <c r="N149" s="11"/>
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A150" s="15"/>
+      <c r="A150" s="12"/>
       <c r="B150" s="8"/>
       <c r="C150" s="8"/>
       <c r="D150" s="8"/>
@@ -4521,7 +4543,7 @@
       <c r="N150" s="11"/>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A151" s="15"/>
+      <c r="A151" s="12"/>
       <c r="B151" s="8"/>
       <c r="C151" s="8"/>
       <c r="D151" s="8"/>
@@ -4543,7 +4565,7 @@
       <c r="N151" s="11"/>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A152" s="15"/>
+      <c r="A152" s="12"/>
       <c r="B152" s="8"/>
       <c r="C152" s="8"/>
       <c r="D152" s="8"/>
@@ -4565,7 +4587,7 @@
       <c r="N152" s="11"/>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A153" s="15"/>
+      <c r="A153" s="12"/>
       <c r="B153" s="8"/>
       <c r="C153" s="8"/>
       <c r="D153" s="8"/>
@@ -4587,7 +4609,7 @@
       <c r="N153" s="11"/>
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A154" s="15"/>
+      <c r="A154" s="12"/>
       <c r="B154" s="8"/>
       <c r="C154" s="8"/>
       <c r="D154" s="8"/>
@@ -4609,7 +4631,7 @@
       <c r="N154" s="11"/>
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A155" s="15"/>
+      <c r="A155" s="12"/>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
       <c r="D155" s="8"/>
@@ -4631,7 +4653,7 @@
       <c r="N155" s="11"/>
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A156" s="15"/>
+      <c r="A156" s="12"/>
       <c r="B156" s="8"/>
       <c r="C156" s="8"/>
       <c r="D156" s="8"/>
@@ -4653,7 +4675,7 @@
       <c r="N156" s="11"/>
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A157" s="15"/>
+      <c r="A157" s="12"/>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
       <c r="D157" s="8"/>
@@ -4675,7 +4697,7 @@
       <c r="N157" s="11"/>
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A158" s="15"/>
+      <c r="A158" s="12"/>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
       <c r="D158" s="8"/>
@@ -4697,7 +4719,7 @@
       <c r="N158" s="11"/>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A159" s="15"/>
+      <c r="A159" s="12"/>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
       <c r="D159" s="8"/>
@@ -4719,7 +4741,7 @@
       <c r="N159" s="11"/>
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A160" s="15"/>
+      <c r="A160" s="12"/>
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
       <c r="D160" s="8"/>
@@ -4741,7 +4763,7 @@
       <c r="N160" s="11"/>
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A161" s="15"/>
+      <c r="A161" s="12"/>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
       <c r="D161" s="8"/>
@@ -4763,7 +4785,7 @@
       <c r="N161" s="11"/>
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A162" s="15"/>
+      <c r="A162" s="12"/>
       <c r="B162" s="8"/>
       <c r="C162" s="8"/>
       <c r="D162" s="8"/>
@@ -4785,7 +4807,7 @@
       <c r="N162" s="11"/>
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A163" s="15"/>
+      <c r="A163" s="12"/>
       <c r="B163" s="8"/>
       <c r="C163" s="8"/>
       <c r="D163" s="8"/>
@@ -4807,7 +4829,7 @@
       <c r="N163" s="11"/>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A164" s="15"/>
+      <c r="A164" s="12"/>
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
       <c r="D164" s="8"/>
@@ -4829,7 +4851,7 @@
       <c r="N164" s="11"/>
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A165" s="15"/>
+      <c r="A165" s="12"/>
       <c r="B165" s="8"/>
       <c r="C165" s="8"/>
       <c r="D165" s="8"/>
@@ -4851,7 +4873,7 @@
       <c r="N165" s="11"/>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A166" s="15"/>
+      <c r="A166" s="12"/>
       <c r="B166" s="8"/>
       <c r="C166" s="8"/>
       <c r="D166" s="8"/>
@@ -4873,7 +4895,7 @@
       <c r="N166" s="11"/>
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A167" s="15"/>
+      <c r="A167" s="12"/>
       <c r="B167" s="8"/>
       <c r="C167" s="8"/>
       <c r="D167" s="8"/>
@@ -4895,7 +4917,7 @@
       <c r="N167" s="11"/>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A168" s="15"/>
+      <c r="A168" s="12"/>
       <c r="B168" s="8"/>
       <c r="C168" s="8"/>
       <c r="D168" s="8"/>
@@ -4917,7 +4939,7 @@
       <c r="N168" s="11"/>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A169" s="15"/>
+      <c r="A169" s="12"/>
       <c r="B169" s="8"/>
       <c r="C169" s="8"/>
       <c r="D169" s="8"/>
@@ -4939,7 +4961,7 @@
       <c r="N169" s="11"/>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A170" s="15"/>
+      <c r="A170" s="12"/>
       <c r="B170" s="8"/>
       <c r="C170" s="8"/>
       <c r="D170" s="8"/>
@@ -4961,7 +4983,7 @@
       <c r="N170" s="11"/>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A171" s="15"/>
+      <c r="A171" s="12"/>
       <c r="B171" s="8"/>
       <c r="C171" s="8"/>
       <c r="D171" s="8"/>
@@ -4983,7 +5005,7 @@
       <c r="N171" s="11"/>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A172" s="15"/>
+      <c r="A172" s="12"/>
       <c r="B172" s="8"/>
       <c r="C172" s="8"/>
       <c r="D172" s="8"/>
@@ -5005,7 +5027,7 @@
       <c r="N172" s="11"/>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A173" s="15"/>
+      <c r="A173" s="12"/>
       <c r="B173" s="8"/>
       <c r="C173" s="8"/>
       <c r="D173" s="8"/>
@@ -5027,7 +5049,7 @@
       <c r="N173" s="11"/>
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A174" s="15"/>
+      <c r="A174" s="12"/>
       <c r="B174" s="8"/>
       <c r="C174" s="8"/>
       <c r="D174" s="8"/>
@@ -5049,7 +5071,7 @@
       <c r="N174" s="11"/>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A175" s="15"/>
+      <c r="A175" s="12"/>
       <c r="B175" s="8"/>
       <c r="C175" s="8"/>
       <c r="D175" s="8"/>
@@ -5071,7 +5093,7 @@
       <c r="N175" s="11"/>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A176" s="15"/>
+      <c r="A176" s="12"/>
       <c r="B176" s="8"/>
       <c r="C176" s="8"/>
       <c r="D176" s="8"/>
@@ -5093,7 +5115,7 @@
       <c r="N176" s="11"/>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A177" s="15"/>
+      <c r="A177" s="12"/>
       <c r="B177" s="8"/>
       <c r="C177" s="8"/>
       <c r="D177" s="8"/>
@@ -5115,7 +5137,7 @@
       <c r="N177" s="11"/>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A178" s="15"/>
+      <c r="A178" s="12"/>
       <c r="B178" s="8"/>
       <c r="C178" s="8"/>
       <c r="D178" s="8"/>
@@ -5137,7 +5159,7 @@
       <c r="N178" s="11"/>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A179" s="15"/>
+      <c r="A179" s="12"/>
       <c r="B179" s="8"/>
       <c r="C179" s="8"/>
       <c r="D179" s="8"/>
@@ -5159,7 +5181,7 @@
       <c r="N179" s="11"/>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A180" s="15"/>
+      <c r="A180" s="12"/>
       <c r="B180" s="8"/>
       <c r="C180" s="8"/>
       <c r="D180" s="8"/>
@@ -5181,7 +5203,7 @@
       <c r="N180" s="11"/>
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A181" s="15"/>
+      <c r="A181" s="12"/>
       <c r="B181" s="8"/>
       <c r="C181" s="8"/>
       <c r="D181" s="8"/>
@@ -5203,7 +5225,7 @@
       <c r="N181" s="11"/>
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A182" s="15"/>
+      <c r="A182" s="12"/>
       <c r="B182" s="8"/>
       <c r="C182" s="8"/>
       <c r="D182" s="8"/>
@@ -5225,7 +5247,7 @@
       <c r="N182" s="11"/>
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A183" s="15"/>
+      <c r="A183" s="12"/>
       <c r="B183" s="8"/>
       <c r="C183" s="8"/>
       <c r="D183" s="8"/>
@@ -5247,7 +5269,7 @@
       <c r="N183" s="11"/>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A184" s="15"/>
+      <c r="A184" s="12"/>
       <c r="B184" s="8"/>
       <c r="C184" s="8"/>
       <c r="D184" s="8"/>
@@ -5269,7 +5291,7 @@
       <c r="N184" s="11"/>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A185" s="15"/>
+      <c r="A185" s="12"/>
       <c r="B185" s="8"/>
       <c r="C185" s="8"/>
       <c r="D185" s="8"/>
@@ -5291,7 +5313,7 @@
       <c r="N185" s="11"/>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A186" s="15"/>
+      <c r="A186" s="12"/>
       <c r="B186" s="8"/>
       <c r="C186" s="8"/>
       <c r="D186" s="8"/>
@@ -5313,7 +5335,7 @@
       <c r="N186" s="11"/>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A187" s="15"/>
+      <c r="A187" s="12"/>
       <c r="B187" s="8"/>
       <c r="C187" s="8"/>
       <c r="D187" s="8"/>
@@ -5335,7 +5357,7 @@
       <c r="N187" s="11"/>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A188" s="15"/>
+      <c r="A188" s="12"/>
       <c r="B188" s="8"/>
       <c r="C188" s="8"/>
       <c r="D188" s="8"/>
@@ -5357,7 +5379,7 @@
       <c r="N188" s="11"/>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A189" s="15"/>
+      <c r="A189" s="12"/>
       <c r="B189" s="8"/>
       <c r="C189" s="8"/>
       <c r="D189" s="8"/>
@@ -5379,7 +5401,7 @@
       <c r="N189" s="11"/>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A190" s="15"/>
+      <c r="A190" s="12"/>
       <c r="B190" s="8"/>
       <c r="C190" s="8"/>
       <c r="D190" s="8"/>
@@ -5401,7 +5423,7 @@
       <c r="N190" s="11"/>
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A191" s="15"/>
+      <c r="A191" s="12"/>
       <c r="B191" s="8"/>
       <c r="C191" s="8"/>
       <c r="D191" s="8"/>
@@ -5423,7 +5445,7 @@
       <c r="N191" s="11"/>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A192" s="15"/>
+      <c r="A192" s="12"/>
       <c r="B192" s="8"/>
       <c r="C192" s="8"/>
       <c r="D192" s="8"/>
@@ -5445,7 +5467,7 @@
       <c r="N192" s="11"/>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A193" s="15"/>
+      <c r="A193" s="12"/>
       <c r="B193" s="8"/>
       <c r="C193" s="8"/>
       <c r="D193" s="8"/>
@@ -5467,7 +5489,7 @@
       <c r="N193" s="11"/>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A194" s="15"/>
+      <c r="A194" s="12"/>
       <c r="B194" s="8"/>
       <c r="C194" s="8"/>
       <c r="D194" s="8"/>
@@ -5489,7 +5511,7 @@
       <c r="N194" s="11"/>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A195" s="15"/>
+      <c r="A195" s="12"/>
       <c r="B195" s="8"/>
       <c r="C195" s="8"/>
       <c r="D195" s="8"/>
@@ -5511,7 +5533,7 @@
       <c r="N195" s="11"/>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A196" s="15"/>
+      <c r="A196" s="12"/>
       <c r="B196" s="8"/>
       <c r="C196" s="8"/>
       <c r="D196" s="8"/>
@@ -5533,7 +5555,7 @@
       <c r="N196" s="11"/>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A197" s="15"/>
+      <c r="A197" s="12"/>
       <c r="B197" s="8"/>
       <c r="C197" s="8"/>
       <c r="D197" s="8"/>
@@ -5555,7 +5577,7 @@
       <c r="N197" s="11"/>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A198" s="15"/>
+      <c r="A198" s="12"/>
       <c r="B198" s="8"/>
       <c r="C198" s="8"/>
       <c r="D198" s="8"/>
@@ -5577,7 +5599,7 @@
       <c r="N198" s="11"/>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A199" s="15"/>
+      <c r="A199" s="12"/>
       <c r="B199" s="8"/>
       <c r="C199" s="8"/>
       <c r="D199" s="8"/>
@@ -5599,7 +5621,7 @@
       <c r="N199" s="11"/>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A200" s="15"/>
+      <c r="A200" s="12"/>
       <c r="B200" s="8"/>
       <c r="C200" s="8"/>
       <c r="D200" s="8"/>
@@ -5621,7 +5643,7 @@
       <c r="N200" s="11"/>
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A201" s="15"/>
+      <c r="A201" s="12"/>
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
       <c r="D201" s="8"/>
@@ -5643,7 +5665,7 @@
       <c r="N201" s="11"/>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A202" s="15"/>
+      <c r="A202" s="12"/>
       <c r="B202" s="8"/>
       <c r="C202" s="8"/>
       <c r="D202" s="8"/>
@@ -5665,7 +5687,7 @@
       <c r="N202" s="11"/>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A203" s="15"/>
+      <c r="A203" s="12"/>
       <c r="B203" s="8"/>
       <c r="C203" s="8"/>
       <c r="D203" s="8"/>
@@ -5687,7 +5709,7 @@
       <c r="N203" s="11"/>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A204" s="15"/>
+      <c r="A204" s="12"/>
       <c r="B204" s="8"/>
       <c r="C204" s="8"/>
       <c r="D204" s="8"/>
@@ -5709,7 +5731,7 @@
       <c r="N204" s="11"/>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A205" s="15"/>
+      <c r="A205" s="12"/>
       <c r="B205" s="8"/>
       <c r="C205" s="8"/>
       <c r="D205" s="8"/>
@@ -5731,7 +5753,7 @@
       <c r="N205" s="11"/>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A206" s="15"/>
+      <c r="A206" s="12"/>
       <c r="B206" s="8"/>
       <c r="C206" s="8"/>
       <c r="D206" s="8"/>
@@ -5753,7 +5775,7 @@
       <c r="N206" s="11"/>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A207" s="15"/>
+      <c r="A207" s="12"/>
       <c r="B207" s="8"/>
       <c r="C207" s="8"/>
       <c r="D207" s="8"/>
@@ -5775,7 +5797,7 @@
       <c r="N207" s="11"/>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A208" s="15"/>
+      <c r="A208" s="12"/>
       <c r="B208" s="8"/>
       <c r="C208" s="8"/>
       <c r="D208" s="8"/>
@@ -5797,7 +5819,7 @@
       <c r="N208" s="11"/>
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A209" s="15"/>
+      <c r="A209" s="12"/>
       <c r="B209" s="8"/>
       <c r="C209" s="8"/>
       <c r="D209" s="8"/>
@@ -5819,7 +5841,7 @@
       <c r="N209" s="11"/>
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A210" s="15"/>
+      <c r="A210" s="12"/>
       <c r="B210" s="8"/>
       <c r="C210" s="8"/>
       <c r="D210" s="8"/>
@@ -5841,7 +5863,7 @@
       <c r="N210" s="11"/>
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A211" s="15"/>
+      <c r="A211" s="12"/>
       <c r="B211" s="8"/>
       <c r="C211" s="8"/>
       <c r="D211" s="8"/>
@@ -5863,7 +5885,7 @@
       <c r="N211" s="11"/>
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A212" s="15"/>
+      <c r="A212" s="12"/>
       <c r="B212" s="8"/>
       <c r="C212" s="8"/>
       <c r="D212" s="8"/>
@@ -5885,7 +5907,7 @@
       <c r="N212" s="11"/>
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A213" s="15"/>
+      <c r="A213" s="12"/>
       <c r="B213" s="8"/>
       <c r="C213" s="8"/>
       <c r="D213" s="8"/>
@@ -5907,7 +5929,7 @@
       <c r="N213" s="11"/>
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A214" s="15"/>
+      <c r="A214" s="12"/>
       <c r="B214" s="8"/>
       <c r="C214" s="8"/>
       <c r="D214" s="8"/>
@@ -5929,7 +5951,7 @@
       <c r="N214" s="11"/>
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A215" s="15"/>
+      <c r="A215" s="12"/>
       <c r="B215" s="8"/>
       <c r="C215" s="8"/>
       <c r="D215" s="8"/>
@@ -5951,7 +5973,7 @@
       <c r="N215" s="11"/>
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A216" s="15"/>
+      <c r="A216" s="12"/>
       <c r="B216" s="8"/>
       <c r="C216" s="8"/>
       <c r="D216" s="8"/>
@@ -5973,7 +5995,7 @@
       <c r="N216" s="11"/>
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A217" s="15"/>
+      <c r="A217" s="12"/>
       <c r="B217" s="8"/>
       <c r="C217" s="8"/>
       <c r="D217" s="8"/>
@@ -5995,7 +6017,7 @@
       <c r="N217" s="11"/>
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A218" s="15"/>
+      <c r="A218" s="12"/>
       <c r="B218" s="8"/>
       <c r="C218" s="8"/>
       <c r="D218" s="8"/>
@@ -6017,7 +6039,7 @@
       <c r="N218" s="11"/>
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A219" s="15"/>
+      <c r="A219" s="12"/>
       <c r="B219" s="8"/>
       <c r="C219" s="8"/>
       <c r="D219" s="8"/>
@@ -6039,7 +6061,7 @@
       <c r="N219" s="11"/>
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A220" s="15"/>
+      <c r="A220" s="12"/>
       <c r="B220" s="8"/>
       <c r="C220" s="8"/>
       <c r="D220" s="8"/>
@@ -6061,7 +6083,7 @@
       <c r="N220" s="11"/>
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A221" s="15"/>
+      <c r="A221" s="12"/>
       <c r="B221" s="8"/>
       <c r="C221" s="8"/>
       <c r="D221" s="8"/>
@@ -6083,7 +6105,7 @@
       <c r="N221" s="11"/>
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A222" s="15"/>
+      <c r="A222" s="12"/>
       <c r="B222" s="8"/>
       <c r="C222" s="8"/>
       <c r="D222" s="8"/>
@@ -6105,7 +6127,7 @@
       <c r="N222" s="11"/>
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A223" s="15"/>
+      <c r="A223" s="12"/>
       <c r="B223" s="8"/>
       <c r="C223" s="8"/>
       <c r="D223" s="8"/>
@@ -6127,7 +6149,7 @@
       <c r="N223" s="11"/>
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A224" s="15"/>
+      <c r="A224" s="12"/>
       <c r="B224" s="8"/>
       <c r="C224" s="8"/>
       <c r="D224" s="8"/>
@@ -6149,7 +6171,7 @@
       <c r="N224" s="11"/>
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A225" s="15"/>
+      <c r="A225" s="12"/>
       <c r="B225" s="8"/>
       <c r="C225" s="8"/>
       <c r="D225" s="8"/>
@@ -6171,7 +6193,7 @@
       <c r="N225" s="11"/>
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A226" s="15"/>
+      <c r="A226" s="12"/>
       <c r="B226" s="8"/>
       <c r="C226" s="8"/>
       <c r="D226" s="8"/>
@@ -6193,7 +6215,7 @@
       <c r="N226" s="11"/>
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A227" s="15"/>
+      <c r="A227" s="12"/>
       <c r="B227" s="8"/>
       <c r="C227" s="8"/>
       <c r="D227" s="8"/>
@@ -6215,7 +6237,7 @@
       <c r="N227" s="11"/>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A228" s="15"/>
+      <c r="A228" s="12"/>
       <c r="B228" s="8"/>
       <c r="C228" s="8"/>
       <c r="D228" s="8"/>
@@ -6237,7 +6259,7 @@
       <c r="N228" s="11"/>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A229" s="15"/>
+      <c r="A229" s="12"/>
       <c r="B229" s="8"/>
       <c r="C229" s="8"/>
       <c r="D229" s="8"/>
@@ -6259,7 +6281,7 @@
       <c r="N229" s="11"/>
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A230" s="15"/>
+      <c r="A230" s="12"/>
       <c r="B230" s="8"/>
       <c r="C230" s="8"/>
       <c r="D230" s="8"/>
@@ -6281,7 +6303,7 @@
       <c r="N230" s="11"/>
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A231" s="15"/>
+      <c r="A231" s="12"/>
       <c r="B231" s="8"/>
       <c r="C231" s="8"/>
       <c r="D231" s="8"/>
@@ -6303,7 +6325,7 @@
       <c r="N231" s="11"/>
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A232" s="15"/>
+      <c r="A232" s="12"/>
       <c r="B232" s="8"/>
       <c r="C232" s="8"/>
       <c r="D232" s="8"/>
@@ -6325,7 +6347,7 @@
       <c r="N232" s="11"/>
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A233" s="15"/>
+      <c r="A233" s="12"/>
       <c r="B233" s="8"/>
       <c r="C233" s="8"/>
       <c r="D233" s="8"/>
@@ -6347,7 +6369,7 @@
       <c r="N233" s="11"/>
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A234" s="15"/>
+      <c r="A234" s="12"/>
       <c r="B234" s="8"/>
       <c r="C234" s="8"/>
       <c r="D234" s="8"/>
@@ -6369,7 +6391,7 @@
       <c r="N234" s="11"/>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A235" s="15"/>
+      <c r="A235" s="12"/>
       <c r="B235" s="8"/>
       <c r="C235" s="8"/>
       <c r="D235" s="8"/>
@@ -6391,7 +6413,7 @@
       <c r="N235" s="11"/>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A236" s="15"/>
+      <c r="A236" s="12"/>
       <c r="B236" s="8"/>
       <c r="C236" s="8"/>
       <c r="D236" s="8"/>
@@ -6413,7 +6435,7 @@
       <c r="N236" s="11"/>
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A237" s="15"/>
+      <c r="A237" s="12"/>
       <c r="B237" s="8"/>
       <c r="C237" s="8"/>
       <c r="D237" s="8"/>
@@ -6435,7 +6457,7 @@
       <c r="N237" s="11"/>
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A238" s="15"/>
+      <c r="A238" s="12"/>
       <c r="B238" s="8"/>
       <c r="C238" s="8"/>
       <c r="D238" s="8"/>
@@ -6457,7 +6479,7 @@
       <c r="N238" s="11"/>
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A239" s="15"/>
+      <c r="A239" s="12"/>
       <c r="B239" s="8"/>
       <c r="C239" s="8"/>
       <c r="D239" s="8"/>
@@ -6479,7 +6501,7 @@
       <c r="N239" s="11"/>
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A240" s="15"/>
+      <c r="A240" s="12"/>
       <c r="B240" s="8"/>
       <c r="C240" s="8"/>
       <c r="D240" s="8"/>
@@ -6501,7 +6523,7 @@
       <c r="N240" s="11"/>
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A241" s="15"/>
+      <c r="A241" s="12"/>
       <c r="B241" s="8"/>
       <c r="C241" s="8"/>
       <c r="D241" s="8"/>
@@ -6523,7 +6545,7 @@
       <c r="N241" s="11"/>
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A242" s="15"/>
+      <c r="A242" s="12"/>
       <c r="B242" s="8"/>
       <c r="C242" s="8"/>
       <c r="D242" s="8"/>
@@ -6545,7 +6567,7 @@
       <c r="N242" s="11"/>
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A243" s="15"/>
+      <c r="A243" s="12"/>
       <c r="B243" s="8"/>
       <c r="C243" s="8"/>
       <c r="D243" s="8"/>
@@ -6567,7 +6589,7 @@
       <c r="N243" s="11"/>
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A244" s="15"/>
+      <c r="A244" s="12"/>
       <c r="B244" s="8"/>
       <c r="C244" s="8"/>
       <c r="D244" s="8"/>
@@ -6589,7 +6611,7 @@
       <c r="N244" s="11"/>
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A245" s="15"/>
+      <c r="A245" s="12"/>
       <c r="B245" s="8"/>
       <c r="C245" s="8"/>
       <c r="D245" s="8"/>
@@ -6611,7 +6633,7 @@
       <c r="N245" s="11"/>
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A246" s="15"/>
+      <c r="A246" s="12"/>
       <c r="B246" s="8"/>
       <c r="C246" s="8"/>
       <c r="D246" s="8"/>
@@ -6633,7 +6655,7 @@
       <c r="N246" s="11"/>
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A247" s="15"/>
+      <c r="A247" s="12"/>
       <c r="B247" s="8"/>
       <c r="C247" s="8"/>
       <c r="D247" s="8"/>
@@ -6655,7 +6677,7 @@
       <c r="N247" s="11"/>
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A248" s="15"/>
+      <c r="A248" s="12"/>
       <c r="B248" s="8"/>
       <c r="C248" s="8"/>
       <c r="D248" s="8"/>
@@ -6677,7 +6699,7 @@
       <c r="N248" s="11"/>
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A249" s="15"/>
+      <c r="A249" s="12"/>
       <c r="B249" s="8"/>
       <c r="C249" s="8"/>
       <c r="D249" s="8"/>
@@ -6699,7 +6721,7 @@
       <c r="N249" s="11"/>
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A250" s="15"/>
+      <c r="A250" s="12"/>
       <c r="B250" s="8"/>
       <c r="C250" s="8"/>
       <c r="D250" s="8"/>
@@ -6721,7 +6743,7 @@
       <c r="N250" s="11"/>
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A251" s="15"/>
+      <c r="A251" s="12"/>
       <c r="B251" s="8"/>
       <c r="C251" s="8"/>
       <c r="D251" s="8"/>
@@ -6743,7 +6765,7 @@
       <c r="N251" s="11"/>
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A252" s="15"/>
+      <c r="A252" s="12"/>
       <c r="B252" s="8"/>
       <c r="C252" s="8"/>
       <c r="D252" s="8"/>
@@ -6765,7 +6787,7 @@
       <c r="N252" s="11"/>
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A253" s="15"/>
+      <c r="A253" s="12"/>
       <c r="B253" s="8"/>
       <c r="C253" s="8"/>
       <c r="D253" s="8"/>
@@ -6787,7 +6809,7 @@
       <c r="N253" s="11"/>
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A254" s="15"/>
+      <c r="A254" s="12"/>
       <c r="B254" s="8"/>
       <c r="C254" s="8"/>
       <c r="D254" s="8"/>
@@ -6809,7 +6831,7 @@
       <c r="N254" s="11"/>
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A255" s="15"/>
+      <c r="A255" s="12"/>
       <c r="B255" s="8"/>
       <c r="C255" s="8"/>
       <c r="D255" s="8"/>
@@ -6831,7 +6853,7 @@
       <c r="N255" s="11"/>
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A256" s="15"/>
+      <c r="A256" s="12"/>
       <c r="B256" s="8"/>
       <c r="C256" s="8"/>
       <c r="D256" s="8"/>
@@ -6853,7 +6875,7 @@
       <c r="N256" s="11"/>
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A257" s="15"/>
+      <c r="A257" s="12"/>
       <c r="B257" s="8"/>
       <c r="C257" s="8"/>
       <c r="D257" s="8"/>
@@ -6875,7 +6897,7 @@
       <c r="N257" s="11"/>
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A258" s="15"/>
+      <c r="A258" s="12"/>
       <c r="B258" s="8"/>
       <c r="C258" s="8"/>
       <c r="D258" s="8"/>
@@ -6897,7 +6919,7 @@
       <c r="N258" s="11"/>
     </row>
     <row r="259" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A259" s="15"/>
+      <c r="A259" s="12"/>
       <c r="B259" s="8"/>
       <c r="C259" s="8"/>
       <c r="D259" s="8"/>
@@ -6919,7 +6941,7 @@
       <c r="N259" s="11"/>
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A260" s="15"/>
+      <c r="A260" s="12"/>
       <c r="B260" s="8"/>
       <c r="C260" s="8"/>
       <c r="D260" s="8"/>
@@ -6941,7 +6963,7 @@
       <c r="N260" s="11"/>
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A261" s="15"/>
+      <c r="A261" s="12"/>
       <c r="B261" s="8"/>
       <c r="C261" s="8"/>
       <c r="D261" s="8"/>
@@ -6963,7 +6985,7 @@
       <c r="N261" s="11"/>
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A262" s="15"/>
+      <c r="A262" s="12"/>
       <c r="B262" s="8"/>
       <c r="C262" s="8"/>
       <c r="D262" s="8"/>
@@ -6985,7 +7007,7 @@
       <c r="N262" s="11"/>
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A263" s="15"/>
+      <c r="A263" s="12"/>
       <c r="B263" s="8"/>
       <c r="C263" s="8"/>
       <c r="D263" s="8"/>
@@ -7007,7 +7029,7 @@
       <c r="N263" s="11"/>
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A264" s="15"/>
+      <c r="A264" s="12"/>
       <c r="B264" s="8"/>
       <c r="C264" s="8"/>
       <c r="D264" s="8"/>
@@ -7029,7 +7051,7 @@
       <c r="N264" s="11"/>
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A265" s="15"/>
+      <c r="A265" s="12"/>
       <c r="B265" s="8"/>
       <c r="C265" s="8"/>
       <c r="D265" s="8"/>
@@ -7051,7 +7073,7 @@
       <c r="N265" s="11"/>
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A266" s="15"/>
+      <c r="A266" s="12"/>
       <c r="B266" s="8"/>
       <c r="C266" s="8"/>
       <c r="D266" s="8"/>
@@ -7073,7 +7095,7 @@
       <c r="N266" s="11"/>
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A267" s="15"/>
+      <c r="A267" s="12"/>
       <c r="B267" s="8"/>
       <c r="C267" s="8"/>
       <c r="D267" s="8"/>
@@ -7095,7 +7117,7 @@
       <c r="N267" s="11"/>
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A268" s="15"/>
+      <c r="A268" s="12"/>
       <c r="B268" s="8"/>
       <c r="C268" s="8"/>
       <c r="D268" s="8"/>
@@ -7117,7 +7139,7 @@
       <c r="N268" s="11"/>
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A269" s="15"/>
+      <c r="A269" s="12"/>
       <c r="B269" s="8"/>
       <c r="C269" s="8"/>
       <c r="D269" s="8"/>
@@ -7139,7 +7161,7 @@
       <c r="N269" s="11"/>
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A270" s="15"/>
+      <c r="A270" s="12"/>
       <c r="B270" s="8"/>
       <c r="C270" s="8"/>
       <c r="D270" s="8"/>
@@ -7161,7 +7183,7 @@
       <c r="N270" s="11"/>
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A271" s="15"/>
+      <c r="A271" s="12"/>
       <c r="B271" s="8"/>
       <c r="C271" s="8"/>
       <c r="D271" s="8"/>
@@ -7183,7 +7205,7 @@
       <c r="N271" s="11"/>
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A272" s="15"/>
+      <c r="A272" s="12"/>
       <c r="B272" s="8"/>
       <c r="C272" s="8"/>
       <c r="D272" s="8"/>
@@ -7205,7 +7227,7 @@
       <c r="N272" s="11"/>
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A273" s="15"/>
+      <c r="A273" s="12"/>
       <c r="B273" s="8"/>
       <c r="C273" s="8"/>
       <c r="D273" s="8"/>
@@ -7227,7 +7249,7 @@
       <c r="N273" s="11"/>
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A274" s="15"/>
+      <c r="A274" s="12"/>
       <c r="B274" s="8"/>
       <c r="C274" s="8"/>
       <c r="D274" s="8"/>
@@ -7249,7 +7271,7 @@
       <c r="N274" s="11"/>
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A275" s="15"/>
+      <c r="A275" s="12"/>
       <c r="B275" s="8"/>
       <c r="C275" s="8"/>
       <c r="D275" s="8"/>
@@ -7271,7 +7293,7 @@
       <c r="N275" s="11"/>
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A276" s="15"/>
+      <c r="A276" s="12"/>
       <c r="B276" s="8"/>
       <c r="C276" s="8"/>
       <c r="D276" s="8"/>
@@ -7293,7 +7315,7 @@
       <c r="N276" s="11"/>
     </row>
     <row r="277" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A277" s="15"/>
+      <c r="A277" s="12"/>
       <c r="B277" s="8"/>
       <c r="C277" s="8"/>
       <c r="D277" s="8"/>
@@ -7315,7 +7337,7 @@
       <c r="N277" s="11"/>
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A278" s="15"/>
+      <c r="A278" s="12"/>
       <c r="B278" s="8"/>
       <c r="C278" s="8"/>
       <c r="D278" s="8"/>
@@ -7337,7 +7359,7 @@
       <c r="N278" s="11"/>
     </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A279" s="15"/>
+      <c r="A279" s="12"/>
       <c r="B279" s="8"/>
       <c r="C279" s="8"/>
       <c r="D279" s="8"/>
@@ -7359,7 +7381,7 @@
       <c r="N279" s="11"/>
     </row>
     <row r="280" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A280" s="15"/>
+      <c r="A280" s="12"/>
       <c r="B280" s="8"/>
       <c r="C280" s="8"/>
       <c r="D280" s="8"/>
@@ -7381,7 +7403,7 @@
       <c r="N280" s="11"/>
     </row>
     <row r="281" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A281" s="15"/>
+      <c r="A281" s="12"/>
       <c r="B281" s="8"/>
       <c r="C281" s="8"/>
       <c r="D281" s="8"/>
@@ -7403,7 +7425,7 @@
       <c r="N281" s="11"/>
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A282" s="15"/>
+      <c r="A282" s="12"/>
       <c r="B282" s="8"/>
       <c r="C282" s="8"/>
       <c r="D282" s="8"/>
@@ -7425,7 +7447,7 @@
       <c r="N282" s="11"/>
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A283" s="15"/>
+      <c r="A283" s="12"/>
       <c r="B283" s="8"/>
       <c r="C283" s="8"/>
       <c r="D283" s="8"/>
@@ -7447,7 +7469,7 @@
       <c r="N283" s="11"/>
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A284" s="15"/>
+      <c r="A284" s="12"/>
       <c r="B284" s="8"/>
       <c r="C284" s="8"/>
       <c r="D284" s="8"/>
@@ -7469,7 +7491,7 @@
       <c r="N284" s="11"/>
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A285" s="15"/>
+      <c r="A285" s="12"/>
       <c r="B285" s="8"/>
       <c r="C285" s="8"/>
       <c r="D285" s="8"/>
@@ -7491,7 +7513,7 @@
       <c r="N285" s="11"/>
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A286" s="15"/>
+      <c r="A286" s="12"/>
       <c r="B286" s="8"/>
       <c r="C286" s="8"/>
       <c r="D286" s="8"/>
@@ -7513,7 +7535,7 @@
       <c r="N286" s="11"/>
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A287" s="15"/>
+      <c r="A287" s="12"/>
       <c r="B287" s="8"/>
       <c r="C287" s="8"/>
       <c r="D287" s="8"/>
@@ -7535,7 +7557,7 @@
       <c r="N287" s="11"/>
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A288" s="15"/>
+      <c r="A288" s="12"/>
       <c r="B288" s="8"/>
       <c r="C288" s="8"/>
       <c r="D288" s="8"/>
@@ -7557,7 +7579,7 @@
       <c r="N288" s="11"/>
     </row>
     <row r="289" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A289" s="15"/>
+      <c r="A289" s="12"/>
       <c r="B289" s="8"/>
       <c r="C289" s="8"/>
       <c r="D289" s="8"/>
@@ -7579,7 +7601,7 @@
       <c r="N289" s="11"/>
     </row>
     <row r="290" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A290" s="15"/>
+      <c r="A290" s="12"/>
       <c r="B290" s="8"/>
       <c r="C290" s="8"/>
       <c r="D290" s="8"/>
@@ -7601,7 +7623,7 @@
       <c r="N290" s="11"/>
     </row>
     <row r="291" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A291" s="15"/>
+      <c r="A291" s="12"/>
       <c r="B291" s="8"/>
       <c r="C291" s="8"/>
       <c r="D291" s="8"/>
@@ -7623,7 +7645,7 @@
       <c r="N291" s="11"/>
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A292" s="15"/>
+      <c r="A292" s="12"/>
       <c r="B292" s="8"/>
       <c r="C292" s="8"/>
       <c r="D292" s="8"/>
@@ -7645,7 +7667,7 @@
       <c r="N292" s="11"/>
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A293" s="15"/>
+      <c r="A293" s="12"/>
       <c r="B293" s="8"/>
       <c r="C293" s="8"/>
       <c r="D293" s="8"/>
@@ -7667,7 +7689,7 @@
       <c r="N293" s="11"/>
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A294" s="15"/>
+      <c r="A294" s="12"/>
       <c r="B294" s="8"/>
       <c r="C294" s="8"/>
       <c r="D294" s="8"/>
@@ -7689,7 +7711,7 @@
       <c r="N294" s="11"/>
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A295" s="15"/>
+      <c r="A295" s="12"/>
       <c r="B295" s="8"/>
       <c r="C295" s="8"/>
       <c r="D295" s="8"/>
@@ -7711,7 +7733,7 @@
       <c r="N295" s="11"/>
     </row>
     <row r="296" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A296" s="15"/>
+      <c r="A296" s="12"/>
       <c r="B296" s="8"/>
       <c r="C296" s="8"/>
       <c r="D296" s="8"/>
@@ -7733,7 +7755,7 @@
       <c r="N296" s="11"/>
     </row>
     <row r="297" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A297" s="15"/>
+      <c r="A297" s="12"/>
       <c r="B297" s="8"/>
       <c r="C297" s="8"/>
       <c r="D297" s="8"/>
@@ -7755,7 +7777,7 @@
       <c r="N297" s="11"/>
     </row>
     <row r="298" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A298" s="15"/>
+      <c r="A298" s="12"/>
       <c r="B298" s="8"/>
       <c r="C298" s="8"/>
       <c r="D298" s="8"/>
@@ -7777,7 +7799,7 @@
       <c r="N298" s="11"/>
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A299" s="15"/>
+      <c r="A299" s="12"/>
       <c r="B299" s="8"/>
       <c r="C299" s="8"/>
       <c r="D299" s="8"/>
@@ -7799,7 +7821,7 @@
       <c r="N299" s="11"/>
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A300" s="15"/>
+      <c r="A300" s="12"/>
       <c r="B300" s="8"/>
       <c r="C300" s="8"/>
       <c r="D300" s="8"/>
@@ -7821,7 +7843,7 @@
       <c r="N300" s="11"/>
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A301" s="15"/>
+      <c r="A301" s="12"/>
       <c r="B301" s="8"/>
       <c r="C301" s="8"/>
       <c r="D301" s="8"/>
@@ -7843,7 +7865,7 @@
       <c r="N301" s="11"/>
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A302" s="15"/>
+      <c r="A302" s="12"/>
       <c r="B302" s="8"/>
       <c r="C302" s="8"/>
       <c r="D302" s="8"/>
@@ -7865,7 +7887,7 @@
       <c r="N302" s="11"/>
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A303" s="15"/>
+      <c r="A303" s="12"/>
       <c r="B303" s="8"/>
       <c r="C303" s="8"/>
       <c r="D303" s="8"/>
@@ -7887,7 +7909,7 @@
       <c r="N303" s="11"/>
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A304" s="15"/>
+      <c r="A304" s="12"/>
       <c r="B304" s="8"/>
       <c r="C304" s="8"/>
       <c r="D304" s="8"/>
@@ -7909,7 +7931,7 @@
       <c r="N304" s="11"/>
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A305" s="15"/>
+      <c r="A305" s="12"/>
       <c r="B305" s="8"/>
       <c r="C305" s="8"/>
       <c r="D305" s="8"/>
@@ -7931,7 +7953,7 @@
       <c r="N305" s="11"/>
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A306" s="15"/>
+      <c r="A306" s="12"/>
       <c r="B306" s="8"/>
       <c r="C306" s="8"/>
       <c r="D306" s="8"/>
@@ -7953,7 +7975,7 @@
       <c r="N306" s="11"/>
     </row>
     <row r="307" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A307" s="15"/>
+      <c r="A307" s="12"/>
       <c r="B307" s="8"/>
       <c r="C307" s="8"/>
       <c r="D307" s="8"/>
@@ -7975,7 +7997,7 @@
       <c r="N307" s="11"/>
     </row>
     <row r="308" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A308" s="15"/>
+      <c r="A308" s="12"/>
       <c r="B308" s="8"/>
       <c r="C308" s="8"/>
       <c r="D308" s="8"/>
@@ -7997,7 +8019,7 @@
       <c r="N308" s="11"/>
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A309" s="15"/>
+      <c r="A309" s="12"/>
       <c r="B309" s="8"/>
       <c r="C309" s="8"/>
       <c r="D309" s="8"/>
@@ -8019,7 +8041,7 @@
       <c r="N309" s="11"/>
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A310" s="15"/>
+      <c r="A310" s="12"/>
       <c r="B310" s="8"/>
       <c r="C310" s="8"/>
       <c r="D310" s="8"/>
@@ -8041,7 +8063,7 @@
       <c r="N310" s="11"/>
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A311" s="15"/>
+      <c r="A311" s="12"/>
       <c r="B311" s="8"/>
       <c r="C311" s="8"/>
       <c r="D311" s="8"/>
@@ -8063,7 +8085,7 @@
       <c r="N311" s="11"/>
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A312" s="15"/>
+      <c r="A312" s="12"/>
       <c r="B312" s="8"/>
       <c r="C312" s="8"/>
       <c r="D312" s="8"/>
@@ -8085,7 +8107,7 @@
       <c r="N312" s="11"/>
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A313" s="15"/>
+      <c r="A313" s="12"/>
       <c r="B313" s="8"/>
       <c r="C313" s="8"/>
       <c r="D313" s="8"/>
@@ -8107,7 +8129,7 @@
       <c r="N313" s="11"/>
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A314" s="15"/>
+      <c r="A314" s="12"/>
       <c r="B314" s="8"/>
       <c r="C314" s="8"/>
       <c r="D314" s="8"/>
@@ -8129,7 +8151,7 @@
       <c r="N314" s="11"/>
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A315" s="15"/>
+      <c r="A315" s="12"/>
       <c r="B315" s="8"/>
       <c r="C315" s="8"/>
       <c r="D315" s="8"/>
@@ -8151,7 +8173,7 @@
       <c r="N315" s="11"/>
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A316" s="15"/>
+      <c r="A316" s="12"/>
       <c r="B316" s="8"/>
       <c r="C316" s="8"/>
       <c r="D316" s="8"/>
@@ -8173,7 +8195,7 @@
       <c r="N316" s="11"/>
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A317" s="15"/>
+      <c r="A317" s="12"/>
       <c r="B317" s="8"/>
       <c r="C317" s="8"/>
       <c r="D317" s="8"/>
@@ -8195,7 +8217,7 @@
       <c r="N317" s="11"/>
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A318" s="15"/>
+      <c r="A318" s="12"/>
       <c r="B318" s="8"/>
       <c r="C318" s="8"/>
       <c r="D318" s="8"/>
@@ -8217,7 +8239,7 @@
       <c r="N318" s="11"/>
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A319" s="15"/>
+      <c r="A319" s="12"/>
       <c r="B319" s="8"/>
       <c r="C319" s="8"/>
       <c r="D319" s="8"/>
@@ -8239,7 +8261,7 @@
       <c r="N319" s="11"/>
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A320" s="15"/>
+      <c r="A320" s="12"/>
       <c r="B320" s="8"/>
       <c r="C320" s="8"/>
       <c r="D320" s="8"/>
@@ -8261,7 +8283,7 @@
       <c r="N320" s="11"/>
     </row>
     <row r="321" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A321" s="15"/>
+      <c r="A321" s="12"/>
       <c r="B321" s="8"/>
       <c r="C321" s="8"/>
       <c r="D321" s="8"/>
@@ -8283,7 +8305,7 @@
       <c r="N321" s="11"/>
     </row>
     <row r="322" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A322" s="15"/>
+      <c r="A322" s="12"/>
       <c r="B322" s="8"/>
       <c r="C322" s="8"/>
       <c r="D322" s="8"/>
@@ -8305,7 +8327,7 @@
       <c r="N322" s="11"/>
     </row>
     <row r="323" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A323" s="15"/>
+      <c r="A323" s="12"/>
       <c r="B323" s="8"/>
       <c r="C323" s="8"/>
       <c r="D323" s="8"/>
@@ -8327,7 +8349,7 @@
       <c r="N323" s="11"/>
     </row>
     <row r="324" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A324" s="15"/>
+      <c r="A324" s="12"/>
       <c r="B324" s="8"/>
       <c r="C324" s="8"/>
       <c r="D324" s="8"/>
@@ -8349,7 +8371,7 @@
       <c r="N324" s="11"/>
     </row>
     <row r="325" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A325" s="15"/>
+      <c r="A325" s="12"/>
       <c r="B325" s="8"/>
       <c r="C325" s="8"/>
       <c r="D325" s="8"/>
@@ -8371,7 +8393,7 @@
       <c r="N325" s="11"/>
     </row>
     <row r="326" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A326" s="15"/>
+      <c r="A326" s="12"/>
       <c r="B326" s="8"/>
       <c r="C326" s="8"/>
       <c r="D326" s="8"/>
@@ -8393,7 +8415,7 @@
       <c r="N326" s="11"/>
     </row>
     <row r="327" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A327" s="15"/>
+      <c r="A327" s="12"/>
       <c r="B327" s="8"/>
       <c r="C327" s="8"/>
       <c r="D327" s="8"/>
@@ -8415,7 +8437,7 @@
       <c r="N327" s="11"/>
     </row>
     <row r="328" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A328" s="15"/>
+      <c r="A328" s="12"/>
       <c r="B328" s="8"/>
       <c r="C328" s="8"/>
       <c r="D328" s="8"/>
@@ -8437,7 +8459,7 @@
       <c r="N328" s="11"/>
     </row>
     <row r="329" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A329" s="15"/>
+      <c r="A329" s="12"/>
       <c r="B329" s="8"/>
       <c r="C329" s="8"/>
       <c r="D329" s="8"/>
@@ -8459,7 +8481,7 @@
       <c r="N329" s="11"/>
     </row>
     <row r="330" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A330" s="15"/>
+      <c r="A330" s="12"/>
       <c r="B330" s="8"/>
       <c r="C330" s="8"/>
       <c r="D330" s="8"/>
@@ -8481,7 +8503,7 @@
       <c r="N330" s="11"/>
     </row>
     <row r="331" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A331" s="15"/>
+      <c r="A331" s="12"/>
       <c r="B331" s="8"/>
       <c r="C331" s="8"/>
       <c r="D331" s="8"/>
@@ -8503,7 +8525,7 @@
       <c r="N331" s="11"/>
     </row>
     <row r="332" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A332" s="15"/>
+      <c r="A332" s="12"/>
       <c r="B332" s="8"/>
       <c r="C332" s="8"/>
       <c r="D332" s="8"/>
@@ -8525,7 +8547,7 @@
       <c r="N332" s="11"/>
     </row>
     <row r="333" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A333" s="15"/>
+      <c r="A333" s="12"/>
       <c r="B333" s="8"/>
       <c r="C333" s="8"/>
       <c r="D333" s="8"/>
@@ -8547,7 +8569,7 @@
       <c r="N333" s="11"/>
     </row>
     <row r="334" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A334" s="15"/>
+      <c r="A334" s="12"/>
       <c r="B334" s="8"/>
       <c r="C334" s="8"/>
       <c r="D334" s="8"/>
@@ -8569,7 +8591,7 @@
       <c r="N334" s="11"/>
     </row>
     <row r="335" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A335" s="15"/>
+      <c r="A335" s="12"/>
       <c r="B335" s="8"/>
       <c r="C335" s="8"/>
       <c r="D335" s="8"/>
@@ -8591,7 +8613,7 @@
       <c r="N335" s="11"/>
     </row>
     <row r="336" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A336" s="15"/>
+      <c r="A336" s="12"/>
       <c r="B336" s="8"/>
       <c r="C336" s="8"/>
       <c r="D336" s="8"/>
@@ -8613,7 +8635,7 @@
       <c r="N336" s="11"/>
     </row>
     <row r="337" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A337" s="15"/>
+      <c r="A337" s="12"/>
       <c r="B337" s="8"/>
       <c r="C337" s="8"/>
       <c r="D337" s="8"/>
@@ -8635,7 +8657,7 @@
       <c r="N337" s="11"/>
     </row>
     <row r="338" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A338" s="15"/>
+      <c r="A338" s="12"/>
       <c r="B338" s="8"/>
       <c r="C338" s="8"/>
       <c r="D338" s="8"/>
@@ -8657,7 +8679,7 @@
       <c r="N338" s="11"/>
     </row>
     <row r="339" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A339" s="15"/>
+      <c r="A339" s="12"/>
       <c r="B339" s="8"/>
       <c r="C339" s="8"/>
       <c r="D339" s="8"/>
@@ -8679,7 +8701,7 @@
       <c r="N339" s="11"/>
     </row>
     <row r="340" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A340" s="15"/>
+      <c r="A340" s="12"/>
       <c r="B340" s="8"/>
       <c r="C340" s="8"/>
       <c r="D340" s="8"/>
@@ -8701,7 +8723,7 @@
       <c r="N340" s="11"/>
     </row>
     <row r="341" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A341" s="15"/>
+      <c r="A341" s="12"/>
       <c r="B341" s="8"/>
       <c r="C341" s="8"/>
       <c r="D341" s="8"/>
@@ -8723,7 +8745,7 @@
       <c r="N341" s="11"/>
     </row>
     <row r="342" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A342" s="15"/>
+      <c r="A342" s="12"/>
       <c r="B342" s="8"/>
       <c r="C342" s="8"/>
       <c r="D342" s="8"/>
@@ -8745,7 +8767,7 @@
       <c r="N342" s="11"/>
     </row>
     <row r="343" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A343" s="15"/>
+      <c r="A343" s="12"/>
       <c r="B343" s="8"/>
       <c r="C343" s="8"/>
       <c r="D343" s="8"/>
@@ -8767,7 +8789,7 @@
       <c r="N343" s="11"/>
     </row>
     <row r="344" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A344" s="15"/>
+      <c r="A344" s="12"/>
       <c r="B344" s="8"/>
       <c r="C344" s="8"/>
       <c r="D344" s="8"/>
@@ -8789,7 +8811,7 @@
       <c r="N344" s="11"/>
     </row>
     <row r="345" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A345" s="15"/>
+      <c r="A345" s="12"/>
       <c r="B345" s="8"/>
       <c r="C345" s="8"/>
       <c r="D345" s="8"/>
@@ -8811,7 +8833,7 @@
       <c r="N345" s="11"/>
     </row>
     <row r="346" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A346" s="15"/>
+      <c r="A346" s="12"/>
       <c r="B346" s="8"/>
       <c r="C346" s="8"/>
       <c r="D346" s="8"/>
@@ -8833,7 +8855,7 @@
       <c r="N346" s="11"/>
     </row>
     <row r="347" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A347" s="15"/>
+      <c r="A347" s="12"/>
       <c r="B347" s="8"/>
       <c r="C347" s="8"/>
       <c r="D347" s="8"/>
@@ -8855,7 +8877,7 @@
       <c r="N347" s="11"/>
     </row>
     <row r="348" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A348" s="15"/>
+      <c r="A348" s="12"/>
       <c r="B348" s="8"/>
       <c r="C348" s="8"/>
       <c r="D348" s="8"/>
@@ -8877,7 +8899,7 @@
       <c r="N348" s="11"/>
     </row>
     <row r="349" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A349" s="15"/>
+      <c r="A349" s="12"/>
       <c r="B349" s="8"/>
       <c r="C349" s="8"/>
       <c r="D349" s="8"/>
@@ -8899,7 +8921,7 @@
       <c r="N349" s="11"/>
     </row>
     <row r="350" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A350" s="15"/>
+      <c r="A350" s="12"/>
       <c r="B350" s="8"/>
       <c r="C350" s="8"/>
       <c r="D350" s="8"/>
@@ -8921,7 +8943,7 @@
       <c r="N350" s="11"/>
     </row>
     <row r="351" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A351" s="15"/>
+      <c r="A351" s="12"/>
       <c r="B351" s="8"/>
       <c r="C351" s="8"/>
       <c r="D351" s="8"/>
@@ -8943,7 +8965,7 @@
       <c r="N351" s="11"/>
     </row>
     <row r="352" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A352" s="15"/>
+      <c r="A352" s="12"/>
       <c r="B352" s="8"/>
       <c r="C352" s="8"/>
       <c r="D352" s="8"/>
@@ -8965,7 +8987,7 @@
       <c r="N352" s="11"/>
     </row>
     <row r="353" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A353" s="15"/>
+      <c r="A353" s="12"/>
       <c r="B353" s="8"/>
       <c r="C353" s="8"/>
       <c r="D353" s="8"/>
@@ -8987,7 +9009,7 @@
       <c r="N353" s="11"/>
     </row>
     <row r="354" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A354" s="15"/>
+      <c r="A354" s="12"/>
       <c r="B354" s="8"/>
       <c r="C354" s="8"/>
       <c r="D354" s="8"/>
@@ -9009,7 +9031,7 @@
       <c r="N354" s="11"/>
     </row>
     <row r="355" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A355" s="15"/>
+      <c r="A355" s="12"/>
       <c r="B355" s="8"/>
       <c r="C355" s="8"/>
       <c r="D355" s="8"/>
@@ -9031,7 +9053,7 @@
       <c r="N355" s="11"/>
     </row>
     <row r="356" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A356" s="15"/>
+      <c r="A356" s="12"/>
       <c r="B356" s="8"/>
       <c r="C356" s="8"/>
       <c r="D356" s="8"/>
@@ -9053,7 +9075,7 @@
       <c r="N356" s="11"/>
     </row>
     <row r="357" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A357" s="15"/>
+      <c r="A357" s="12"/>
       <c r="B357" s="8"/>
       <c r="C357" s="8"/>
       <c r="D357" s="8"/>
@@ -9075,7 +9097,7 @@
       <c r="N357" s="11"/>
     </row>
     <row r="358" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A358" s="15"/>
+      <c r="A358" s="12"/>
       <c r="B358" s="8"/>
       <c r="C358" s="8"/>
       <c r="D358" s="8"/>
@@ -9097,7 +9119,7 @@
       <c r="N358" s="11"/>
     </row>
     <row r="359" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A359" s="15"/>
+      <c r="A359" s="12"/>
       <c r="B359" s="8"/>
       <c r="C359" s="8"/>
       <c r="D359" s="8"/>
@@ -9119,7 +9141,7 @@
       <c r="N359" s="11"/>
     </row>
     <row r="360" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A360" s="15"/>
+      <c r="A360" s="12"/>
       <c r="B360" s="8"/>
       <c r="C360" s="8"/>
       <c r="D360" s="8"/>
@@ -9141,7 +9163,7 @@
       <c r="N360" s="11"/>
     </row>
     <row r="361" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A361" s="15"/>
+      <c r="A361" s="12"/>
       <c r="B361" s="8"/>
       <c r="C361" s="8"/>
       <c r="D361" s="8"/>
@@ -9163,7 +9185,7 @@
       <c r="N361" s="11"/>
     </row>
     <row r="362" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A362" s="15"/>
+      <c r="A362" s="12"/>
       <c r="B362" s="8"/>
       <c r="C362" s="8"/>
       <c r="D362" s="8"/>
@@ -9185,7 +9207,7 @@
       <c r="N362" s="11"/>
     </row>
     <row r="363" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A363" s="15"/>
+      <c r="A363" s="12"/>
       <c r="B363" s="8"/>
       <c r="C363" s="8"/>
       <c r="D363" s="8"/>
@@ -9207,7 +9229,7 @@
       <c r="N363" s="11"/>
     </row>
     <row r="364" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A364" s="15"/>
+      <c r="A364" s="12"/>
       <c r="B364" s="8"/>
       <c r="C364" s="8"/>
       <c r="D364" s="8"/>
@@ -9229,7 +9251,7 @@
       <c r="N364" s="11"/>
     </row>
     <row r="365" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A365" s="15"/>
+      <c r="A365" s="12"/>
       <c r="B365" s="8"/>
       <c r="C365" s="8"/>
       <c r="D365" s="8"/>
@@ -9251,7 +9273,7 @@
       <c r="N365" s="11"/>
     </row>
     <row r="366" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A366" s="15"/>
+      <c r="A366" s="12"/>
       <c r="B366" s="8"/>
       <c r="C366" s="8"/>
       <c r="D366" s="8"/>
@@ -9273,7 +9295,7 @@
       <c r="N366" s="11"/>
     </row>
     <row r="367" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A367" s="15"/>
+      <c r="A367" s="12"/>
       <c r="B367" s="8"/>
       <c r="C367" s="8"/>
       <c r="D367" s="8"/>
@@ -9295,7 +9317,7 @@
       <c r="N367" s="11"/>
     </row>
     <row r="368" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A368" s="15"/>
+      <c r="A368" s="12"/>
       <c r="B368" s="8"/>
       <c r="C368" s="8"/>
       <c r="D368" s="8"/>
@@ -9317,7 +9339,7 @@
       <c r="N368" s="11"/>
     </row>
     <row r="369" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A369" s="15"/>
+      <c r="A369" s="12"/>
       <c r="B369" s="8"/>
       <c r="C369" s="8"/>
       <c r="D369" s="8"/>
@@ -9339,7 +9361,7 @@
       <c r="N369" s="11"/>
     </row>
     <row r="370" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A370" s="15"/>
+      <c r="A370" s="12"/>
       <c r="B370" s="8"/>
       <c r="C370" s="8"/>
       <c r="D370" s="8"/>
@@ -9361,7 +9383,7 @@
       <c r="N370" s="11"/>
     </row>
     <row r="371" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A371" s="15"/>
+      <c r="A371" s="12"/>
       <c r="B371" s="8"/>
       <c r="C371" s="8"/>
       <c r="D371" s="8"/>
@@ -9383,7 +9405,7 @@
       <c r="N371" s="11"/>
     </row>
     <row r="372" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A372" s="15"/>
+      <c r="A372" s="12"/>
       <c r="B372" s="8"/>
       <c r="C372" s="8"/>
       <c r="D372" s="8"/>
@@ -9405,7 +9427,7 @@
       <c r="N372" s="11"/>
     </row>
     <row r="373" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A373" s="15"/>
+      <c r="A373" s="12"/>
       <c r="B373" s="8"/>
       <c r="C373" s="8"/>
       <c r="D373" s="8"/>
@@ -9427,7 +9449,7 @@
       <c r="N373" s="11"/>
     </row>
     <row r="374" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A374" s="15"/>
+      <c r="A374" s="12"/>
       <c r="B374" s="8"/>
       <c r="C374" s="8"/>
       <c r="D374" s="8"/>
@@ -9449,7 +9471,7 @@
       <c r="N374" s="11"/>
     </row>
     <row r="375" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A375" s="15"/>
+      <c r="A375" s="12"/>
       <c r="B375" s="8"/>
       <c r="C375" s="8"/>
       <c r="D375" s="8"/>
@@ -9471,7 +9493,7 @@
       <c r="N375" s="11"/>
     </row>
     <row r="376" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A376" s="15"/>
+      <c r="A376" s="12"/>
       <c r="B376" s="8"/>
       <c r="C376" s="8"/>
       <c r="D376" s="8"/>
@@ -9493,7 +9515,7 @@
       <c r="N376" s="11"/>
     </row>
     <row r="377" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A377" s="15"/>
+      <c r="A377" s="12"/>
       <c r="B377" s="8"/>
       <c r="C377" s="8"/>
       <c r="D377" s="8"/>
@@ -9515,7 +9537,7 @@
       <c r="N377" s="11"/>
     </row>
     <row r="378" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A378" s="15"/>
+      <c r="A378" s="12"/>
       <c r="B378" s="8"/>
       <c r="C378" s="8"/>
       <c r="D378" s="8"/>
@@ -9537,7 +9559,7 @@
       <c r="N378" s="11"/>
     </row>
     <row r="379" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A379" s="15"/>
+      <c r="A379" s="12"/>
       <c r="B379" s="8"/>
       <c r="C379" s="8"/>
       <c r="D379" s="8"/>
@@ -9559,7 +9581,7 @@
       <c r="N379" s="11"/>
     </row>
     <row r="380" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A380" s="15"/>
+      <c r="A380" s="12"/>
       <c r="B380" s="8"/>
       <c r="C380" s="8"/>
       <c r="D380" s="8"/>
@@ -9581,7 +9603,7 @@
       <c r="N380" s="11"/>
     </row>
     <row r="381" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A381" s="15"/>
+      <c r="A381" s="12"/>
       <c r="B381" s="8"/>
       <c r="C381" s="8"/>
       <c r="D381" s="8"/>
@@ -9603,7 +9625,7 @@
       <c r="N381" s="11"/>
     </row>
     <row r="382" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A382" s="15"/>
+      <c r="A382" s="12"/>
       <c r="B382" s="8"/>
       <c r="C382" s="8"/>
       <c r="D382" s="8"/>
@@ -9625,7 +9647,7 @@
       <c r="N382" s="11"/>
     </row>
     <row r="383" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A383" s="15"/>
+      <c r="A383" s="12"/>
       <c r="B383" s="8"/>
       <c r="C383" s="8"/>
       <c r="D383" s="8"/>
@@ -9647,7 +9669,7 @@
       <c r="N383" s="11"/>
     </row>
     <row r="384" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A384" s="15"/>
+      <c r="A384" s="12"/>
       <c r="B384" s="8"/>
       <c r="C384" s="8"/>
       <c r="D384" s="8"/>
@@ -9669,7 +9691,7 @@
       <c r="N384" s="11"/>
     </row>
     <row r="385" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A385" s="15"/>
+      <c r="A385" s="12"/>
       <c r="B385" s="8"/>
       <c r="C385" s="8"/>
       <c r="D385" s="8"/>
@@ -9691,7 +9713,7 @@
       <c r="N385" s="11"/>
     </row>
     <row r="386" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A386" s="15"/>
+      <c r="A386" s="12"/>
       <c r="B386" s="8"/>
       <c r="C386" s="8"/>
       <c r="D386" s="8"/>
@@ -9713,7 +9735,7 @@
       <c r="N386" s="11"/>
     </row>
     <row r="387" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A387" s="15"/>
+      <c r="A387" s="12"/>
       <c r="B387" s="8"/>
       <c r="C387" s="8"/>
       <c r="D387" s="8"/>
@@ -9735,7 +9757,7 @@
       <c r="N387" s="11"/>
     </row>
     <row r="388" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A388" s="15"/>
+      <c r="A388" s="12"/>
       <c r="B388" s="8"/>
       <c r="C388" s="8"/>
       <c r="D388" s="8"/>
@@ -9757,7 +9779,7 @@
       <c r="N388" s="11"/>
     </row>
     <row r="389" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A389" s="15"/>
+      <c r="A389" s="12"/>
       <c r="B389" s="8"/>
       <c r="C389" s="8"/>
       <c r="D389" s="8"/>
@@ -9779,7 +9801,7 @@
       <c r="N389" s="11"/>
     </row>
     <row r="390" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A390" s="15"/>
+      <c r="A390" s="12"/>
       <c r="B390" s="8"/>
       <c r="C390" s="8"/>
       <c r="D390" s="8"/>
@@ -9801,7 +9823,7 @@
       <c r="N390" s="11"/>
     </row>
     <row r="391" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A391" s="15"/>
+      <c r="A391" s="12"/>
       <c r="B391" s="8"/>
       <c r="C391" s="8"/>
       <c r="D391" s="8"/>
@@ -9823,7 +9845,7 @@
       <c r="N391" s="11"/>
     </row>
     <row r="392" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A392" s="15"/>
+      <c r="A392" s="12"/>
       <c r="B392" s="8"/>
       <c r="C392" s="8"/>
       <c r="D392" s="8"/>
@@ -9845,7 +9867,7 @@
       <c r="N392" s="11"/>
     </row>
     <row r="393" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A393" s="15"/>
+      <c r="A393" s="12"/>
       <c r="B393" s="8"/>
       <c r="C393" s="8"/>
       <c r="D393" s="8"/>
@@ -9867,7 +9889,7 @@
       <c r="N393" s="11"/>
     </row>
     <row r="394" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A394" s="15"/>
+      <c r="A394" s="12"/>
       <c r="B394" s="8"/>
       <c r="C394" s="8"/>
       <c r="D394" s="8"/>
@@ -9889,7 +9911,7 @@
       <c r="N394" s="11"/>
     </row>
     <row r="395" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A395" s="15"/>
+      <c r="A395" s="12"/>
       <c r="B395" s="8"/>
       <c r="C395" s="8"/>
       <c r="D395" s="8"/>
@@ -9911,7 +9933,7 @@
       <c r="N395" s="11"/>
     </row>
     <row r="396" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A396" s="15"/>
+      <c r="A396" s="12"/>
       <c r="B396" s="8"/>
       <c r="C396" s="8"/>
       <c r="D396" s="8"/>
@@ -9933,7 +9955,7 @@
       <c r="N396" s="11"/>
     </row>
     <row r="397" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A397" s="15"/>
+      <c r="A397" s="12"/>
       <c r="B397" s="8"/>
       <c r="C397" s="8"/>
       <c r="D397" s="8"/>
@@ -9955,7 +9977,7 @@
       <c r="N397" s="11"/>
     </row>
     <row r="398" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A398" s="15"/>
+      <c r="A398" s="12"/>
       <c r="B398" s="8"/>
       <c r="C398" s="8"/>
       <c r="D398" s="8"/>
@@ -9977,7 +9999,7 @@
       <c r="N398" s="11"/>
     </row>
     <row r="399" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A399" s="15"/>
+      <c r="A399" s="12"/>
       <c r="B399" s="8"/>
       <c r="C399" s="8"/>
       <c r="D399" s="8"/>
@@ -9999,7 +10021,7 @@
       <c r="N399" s="11"/>
     </row>
     <row r="400" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A400" s="15"/>
+      <c r="A400" s="12"/>
       <c r="B400" s="8"/>
       <c r="C400" s="8"/>
       <c r="D400" s="8"/>

--- a/12602477.xlsx
+++ b/12602477.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1684,28 +1684,52 @@
       <c r="A21" s="12">
         <v>46283</v>
       </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="9" t="str">
+      <c r="B21" s="8">
+        <v>360</v>
+      </c>
+      <c r="C21" s="8">
+        <v>60</v>
+      </c>
+      <c r="D21" s="8">
+        <v>240</v>
+      </c>
+      <c r="E21" s="8">
+        <v>180</v>
+      </c>
+      <c r="F21" s="8">
+        <v>0</v>
+      </c>
+      <c r="G21" s="8">
+        <v>0</v>
+      </c>
+      <c r="H21" s="8">
+        <v>240</v>
+      </c>
+      <c r="I21" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="9" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J21" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="11"/>
+        <v>360</v>
+      </c>
+      <c r="K21" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L21" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="M21" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="N21" s="16" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="12"/>
+      <c r="A22" s="12">
+        <v>46285</v>
+      </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>

--- a/12602477.xlsx
+++ b/12602477.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1730,25 +1730,47 @@
       <c r="A22" s="12">
         <v>46285</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="9" t="str">
+      <c r="B22" s="8">
+        <v>420</v>
+      </c>
+      <c r="C22" s="8">
+        <v>45</v>
+      </c>
+      <c r="D22" s="8">
+        <v>180</v>
+      </c>
+      <c r="E22" s="8">
+        <v>120</v>
+      </c>
+      <c r="F22" s="8">
+        <v>0</v>
+      </c>
+      <c r="G22" s="8">
+        <v>0</v>
+      </c>
+      <c r="H22" s="8">
+        <v>240</v>
+      </c>
+      <c r="I22" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="9" t="str">
+        <v>1005</v>
+      </c>
+      <c r="J22" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="11"/>
+        <v>435</v>
+      </c>
+      <c r="K22" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L22" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="M22" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="N22" s="16" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="12"/>

--- a/12602477.xlsx
+++ b/12602477.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1773,73 +1773,147 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="12"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="9" t="str">
+      <c r="A23" s="12">
+        <v>46287</v>
+      </c>
+      <c r="B23" s="8">
+        <v>300</v>
+      </c>
+      <c r="C23" s="8">
+        <v>60</v>
+      </c>
+      <c r="D23" s="8">
+        <v>60</v>
+      </c>
+      <c r="E23" s="8">
+        <v>120</v>
+      </c>
+      <c r="F23" s="8">
+        <v>350</v>
+      </c>
+      <c r="G23" s="8">
+        <v>7</v>
+      </c>
+      <c r="H23" s="8">
+        <v>240</v>
+      </c>
+      <c r="I23" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="9" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J23" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="11"/>
+        <v>310</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M23" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="N23" s="16" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="12"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="9" t="str">
+      <c r="A24" s="12">
+        <v>46289</v>
+      </c>
+      <c r="B24" s="8">
+        <v>360</v>
+      </c>
+      <c r="C24" s="8">
+        <v>60</v>
+      </c>
+      <c r="D24" s="8">
+        <v>120</v>
+      </c>
+      <c r="E24" s="8">
+        <v>120</v>
+      </c>
+      <c r="F24" s="8">
+        <v>350</v>
+      </c>
+      <c r="G24" s="8">
+        <v>7</v>
+      </c>
+      <c r="H24" s="8">
+        <v>240</v>
+      </c>
+      <c r="I24" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="9" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J24" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="11"/>
+        <v>190</v>
+      </c>
+      <c r="K24" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="L24" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M24" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="N24" s="16" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="12"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="9" t="str">
+      <c r="A25" s="12">
+        <v>46291</v>
+      </c>
+      <c r="B25" s="8">
+        <v>480</v>
+      </c>
+      <c r="C25" s="8">
+        <v>45</v>
+      </c>
+      <c r="D25" s="8">
+        <v>120</v>
+      </c>
+      <c r="E25" s="8">
+        <v>240</v>
+      </c>
+      <c r="F25" s="8">
+        <v>0</v>
+      </c>
+      <c r="G25" s="8">
+        <v>0</v>
+      </c>
+      <c r="H25" s="8">
+        <v>240</v>
+      </c>
+      <c r="I25" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="9" t="str">
+        <v>1125</v>
+      </c>
+      <c r="J25" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="11"/>
+        <v>315</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L25" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="M25" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="N25" s="16" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="12"/>
+      <c r="A26" s="12">
+        <v>46293</v>
+      </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
@@ -1858,10 +1932,12 @@
       <c r="K26" s="10"/>
       <c r="L26" s="10"/>
       <c r="M26" s="10"/>
-      <c r="N26" s="11"/>
+      <c r="N26" s="16"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="12"/>
+      <c r="A27" s="12">
+        <v>46295</v>
+      </c>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>

--- a/12602477.xlsx
+++ b/12602477.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -227,6 +227,12 @@
   </si>
   <si>
     <t>it was an amazing day</t>
+  </si>
+  <si>
+    <t>it was a neutral day</t>
+  </si>
+  <si>
+    <t>o</t>
   </si>
 </sst>
 </file>
@@ -1914,52 +1920,98 @@
       <c r="A26" s="12">
         <v>46293</v>
       </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="9" t="str">
+      <c r="B26" s="8">
+        <v>480</v>
+      </c>
+      <c r="C26" s="8">
+        <v>45</v>
+      </c>
+      <c r="D26" s="8">
+        <v>120</v>
+      </c>
+      <c r="E26" s="8">
+        <v>240</v>
+      </c>
+      <c r="F26" s="8">
+        <v>0</v>
+      </c>
+      <c r="G26" s="8">
+        <v>0</v>
+      </c>
+      <c r="H26" s="8">
+        <v>240</v>
+      </c>
+      <c r="I26" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="9" t="str">
+        <v>1125</v>
+      </c>
+      <c r="J26" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10"/>
-      <c r="N26" s="16"/>
+        <v>315</v>
+      </c>
+      <c r="K26" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L26" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="M26" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="N26" s="16" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="12">
         <v>46295</v>
       </c>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="9" t="str">
+      <c r="B27" s="13">
+        <v>480</v>
+      </c>
+      <c r="C27" s="13">
+        <v>45</v>
+      </c>
+      <c r="D27" s="8">
+        <v>90</v>
+      </c>
+      <c r="E27" s="8">
+        <v>60</v>
+      </c>
+      <c r="F27" s="8">
+        <v>0</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H27" s="8">
+        <v>480</v>
+      </c>
+      <c r="I27" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="9" t="str">
+        <v>1155</v>
+      </c>
+      <c r="J27" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
-      <c r="N27" s="11"/>
+        <v>285</v>
+      </c>
+      <c r="K27" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="L27" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="M27" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="N27" s="16" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="12"/>
+      <c r="A28" s="12">
+        <v>46296</v>
+      </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
@@ -1975,13 +2027,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K28" s="10"/>
+      <c r="K28" s="15"/>
       <c r="L28" s="10"/>
       <c r="M28" s="10"/>
-      <c r="N28" s="11"/>
+      <c r="N28" s="16"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="12"/>
+      <c r="A29" s="12">
+        <v>46297</v>
+      </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
@@ -2003,7 +2057,9 @@
       <c r="N29" s="11"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="12"/>
+      <c r="A30" s="12">
+        <v>46298</v>
+      </c>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>

--- a/12602477.xlsx
+++ b/12602477.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -230,9 +230,6 @@
   </si>
   <si>
     <t>it was a neutral day</t>
-  </si>
-  <si>
-    <t>o</t>
   </si>
 </sst>
 </file>
@@ -1981,8 +1978,8 @@
       <c r="F27" s="8">
         <v>0</v>
       </c>
-      <c r="G27" s="8" t="s">
-        <v>70</v>
+      <c r="G27" s="8">
+        <v>0</v>
       </c>
       <c r="H27" s="8">
         <v>480</v>
@@ -2012,49 +2009,93 @@
       <c r="A28" s="12">
         <v>46296</v>
       </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="9" t="str">
+      <c r="B28" s="8">
+        <v>480</v>
+      </c>
+      <c r="C28" s="8">
+        <v>60</v>
+      </c>
+      <c r="D28" s="8">
+        <v>120</v>
+      </c>
+      <c r="E28" s="8">
+        <v>120</v>
+      </c>
+      <c r="F28" s="8">
+        <v>0</v>
+      </c>
+      <c r="G28" s="8">
+        <v>0</v>
+      </c>
+      <c r="H28" s="8">
+        <v>480</v>
+      </c>
+      <c r="I28" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="9" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J28" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="15"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
-      <c r="N28" s="16"/>
+        <v>180</v>
+      </c>
+      <c r="K28" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="L28" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="M28" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="N28" s="16" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="12">
         <v>46297</v>
       </c>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="9" t="str">
+      <c r="B29" s="8">
+        <v>480</v>
+      </c>
+      <c r="C29" s="8">
+        <v>45</v>
+      </c>
+      <c r="D29" s="8">
+        <v>120</v>
+      </c>
+      <c r="E29" s="8">
+        <v>120</v>
+      </c>
+      <c r="F29" s="8">
+        <v>0</v>
+      </c>
+      <c r="G29" s="8">
+        <v>0</v>
+      </c>
+      <c r="H29" s="8">
+        <v>480</v>
+      </c>
+      <c r="I29" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="9" t="str">
+        <v>1245</v>
+      </c>
+      <c r="J29" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="11"/>
+        <v>195</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L29" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="M29" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="N29" s="16" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="12">
@@ -2081,7 +2122,9 @@
       <c r="N30" s="11"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="12"/>
+      <c r="A31" s="12">
+        <v>46299</v>
+      </c>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -2103,7 +2146,9 @@
       <c r="N31" s="11"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="12"/>
+      <c r="A32" s="12">
+        <v>46300</v>
+      </c>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -2125,7 +2170,9 @@
       <c r="N32" s="11"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="12"/>
+      <c r="A33" s="12">
+        <v>46301</v>
+      </c>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -2147,7 +2194,9 @@
       <c r="N33" s="11"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="12"/>
+      <c r="A34" s="12">
+        <v>46302</v>
+      </c>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
@@ -2169,7 +2218,9 @@
       <c r="N34" s="11"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="12"/>
+      <c r="A35" s="12">
+        <v>46303</v>
+      </c>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
@@ -2191,7 +2242,9 @@
       <c r="N35" s="11"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="12"/>
+      <c r="A36" s="12">
+        <v>46304</v>
+      </c>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
@@ -2213,7 +2266,9 @@
       <c r="N36" s="11"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="12"/>
+      <c r="A37" s="12">
+        <v>46305</v>
+      </c>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>

--- a/12602477.xlsx
+++ b/12602477.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sweeti Oli\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sweeti Oli\OneDrive\Desktop\Colleges\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2101,25 +2101,47 @@
       <c r="A30" s="12">
         <v>46298</v>
       </c>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="9" t="str">
+      <c r="B30" s="8">
+        <v>480</v>
+      </c>
+      <c r="C30" s="8">
+        <v>60</v>
+      </c>
+      <c r="D30" s="8">
+        <v>120</v>
+      </c>
+      <c r="E30" s="8">
+        <v>120</v>
+      </c>
+      <c r="F30" s="8">
+        <v>0</v>
+      </c>
+      <c r="G30" s="8">
+        <v>0</v>
+      </c>
+      <c r="H30" s="8">
+        <v>480</v>
+      </c>
+      <c r="I30" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="9" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J30" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
-      <c r="N30" s="11"/>
+        <v>180</v>
+      </c>
+      <c r="K30" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L30" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="M30" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="N30" s="16" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="12">

--- a/12602477.xlsx
+++ b/12602477.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sweeti Oli\OneDrive\Desktop\Colleges\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sweeti Oli\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2147,25 +2147,47 @@
       <c r="A31" s="12">
         <v>46299</v>
       </c>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="9" t="str">
+      <c r="B31" s="13">
+        <v>480</v>
+      </c>
+      <c r="C31" s="13">
+        <v>60</v>
+      </c>
+      <c r="D31" s="8">
+        <v>90</v>
+      </c>
+      <c r="E31" s="8">
+        <v>90</v>
+      </c>
+      <c r="F31" s="8">
+        <v>0</v>
+      </c>
+      <c r="G31" s="8">
+        <v>0</v>
+      </c>
+      <c r="H31" s="8">
+        <v>480</v>
+      </c>
+      <c r="I31" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="9" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J31" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
-      <c r="N31" s="11"/>
+        <v>240</v>
+      </c>
+      <c r="K31" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L31" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="M31" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="N31" s="16" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="12">

--- a/12602477.xlsx
+++ b/12602477.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2193,25 +2193,47 @@
       <c r="A32" s="12">
         <v>46300</v>
       </c>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="9" t="str">
+      <c r="B32" s="13">
+        <v>480</v>
+      </c>
+      <c r="C32" s="13">
+        <v>60</v>
+      </c>
+      <c r="D32" s="13">
+        <v>120</v>
+      </c>
+      <c r="E32" s="8">
+        <v>90</v>
+      </c>
+      <c r="F32" s="8">
+        <v>150</v>
+      </c>
+      <c r="G32" s="8">
+        <v>3</v>
+      </c>
+      <c r="H32" s="8">
+        <v>300</v>
+      </c>
+      <c r="I32" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="9" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J32" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
-      <c r="N32" s="11"/>
+        <v>240</v>
+      </c>
+      <c r="K32" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L32" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="M32" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="N32" s="16" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="12">

--- a/12602477.xlsx
+++ b/12602477.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2239,73 +2239,139 @@
       <c r="A33" s="12">
         <v>46301</v>
       </c>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="9" t="str">
+      <c r="B33" s="13">
+        <v>480</v>
+      </c>
+      <c r="C33" s="13">
+        <v>60</v>
+      </c>
+      <c r="D33" s="13">
+        <v>90</v>
+      </c>
+      <c r="E33" s="13">
+        <v>120</v>
+      </c>
+      <c r="F33" s="8">
+        <v>350</v>
+      </c>
+      <c r="G33" s="8">
+        <v>7</v>
+      </c>
+      <c r="H33" s="8">
+        <v>240</v>
+      </c>
+      <c r="I33" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="9" t="str">
+        <v>1340</v>
+      </c>
+      <c r="J33" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="10"/>
-      <c r="L33" s="10"/>
-      <c r="M33" s="10"/>
-      <c r="N33" s="11"/>
+        <v>100</v>
+      </c>
+      <c r="K33" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L33" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="M33" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="N33" s="16" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="12">
         <v>46302</v>
       </c>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="9" t="str">
+      <c r="B34" s="13">
+        <v>480</v>
+      </c>
+      <c r="C34" s="13">
+        <v>60</v>
+      </c>
+      <c r="D34" s="13">
+        <v>120</v>
+      </c>
+      <c r="E34" s="13">
+        <v>120</v>
+      </c>
+      <c r="F34" s="8">
+        <v>200</v>
+      </c>
+      <c r="G34" s="8">
+        <v>4</v>
+      </c>
+      <c r="H34" s="8">
+        <v>360</v>
+      </c>
+      <c r="I34" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="9" t="str">
+        <v>1340</v>
+      </c>
+      <c r="J34" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="10"/>
-      <c r="L34" s="10"/>
-      <c r="M34" s="10"/>
-      <c r="N34" s="11"/>
+        <v>100</v>
+      </c>
+      <c r="K34" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L34" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="M34" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="N34" s="16" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="12">
         <v>46303</v>
       </c>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="9" t="str">
+      <c r="B35" s="13">
+        <v>480</v>
+      </c>
+      <c r="C35" s="13">
+        <v>60</v>
+      </c>
+      <c r="D35" s="13">
+        <v>120</v>
+      </c>
+      <c r="E35" s="13">
+        <v>90</v>
+      </c>
+      <c r="F35" s="8">
+        <v>0</v>
+      </c>
+      <c r="G35" s="8">
+        <v>0</v>
+      </c>
+      <c r="H35" s="8">
+        <v>480</v>
+      </c>
+      <c r="I35" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="9" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J35" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
-      <c r="N35" s="11"/>
+        <v>210</v>
+      </c>
+      <c r="K35" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L35" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="M35" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="N35" s="16" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="12">

--- a/12602477.xlsx
+++ b/12602477.xlsx
@@ -1,26 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sweeti Oli\OneDrive\Desktop\Colleges\CAP776 MINOR PROJECT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Naman\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7827EE5-8B20-40B5-8F3D-05CF5A9BA7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9780" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -236,12 +250,18 @@
   </si>
   <si>
     <t>it was a neutral day</t>
+  </si>
+  <si>
+    <t>I was travelling so it was okay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I was travelling so I was tiring </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -708,7 +728,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A39"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -899,8 +919,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N115"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:N110"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3157,49 +3177,93 @@
       <c r="A53" s="12">
         <v>46304</v>
       </c>
-      <c r="B53" s="8"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
-      <c r="G53" s="8"/>
-      <c r="H53" s="8"/>
-      <c r="I53" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="10"/>
-      <c r="L53" s="10"/>
-      <c r="M53" s="10"/>
-      <c r="N53" s="11"/>
+      <c r="B53" s="8">
+        <v>480</v>
+      </c>
+      <c r="C53" s="8">
+        <v>60</v>
+      </c>
+      <c r="D53" s="8">
+        <v>0</v>
+      </c>
+      <c r="E53" s="8">
+        <v>0</v>
+      </c>
+      <c r="F53" s="8">
+        <v>0</v>
+      </c>
+      <c r="G53" s="8">
+        <v>0</v>
+      </c>
+      <c r="H53" s="8">
+        <v>720</v>
+      </c>
+      <c r="I53" s="9">
+        <f t="shared" si="0"/>
+        <v>1260</v>
+      </c>
+      <c r="J53" s="9">
+        <f t="shared" si="1"/>
+        <v>180</v>
+      </c>
+      <c r="K53" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="L53" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="M53" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="N53" s="11" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="12">
         <v>46305</v>
       </c>
-      <c r="B54" s="8"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8"/>
-      <c r="H54" s="8"/>
-      <c r="I54" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="10"/>
-      <c r="L54" s="10"/>
-      <c r="M54" s="10"/>
-      <c r="N54" s="11"/>
+      <c r="B54" s="8">
+        <v>240</v>
+      </c>
+      <c r="C54" s="8">
+        <v>30</v>
+      </c>
+      <c r="D54" s="8">
+        <v>0</v>
+      </c>
+      <c r="E54" s="8">
+        <v>0</v>
+      </c>
+      <c r="F54" s="8">
+        <v>0</v>
+      </c>
+      <c r="G54" s="8">
+        <v>0</v>
+      </c>
+      <c r="H54" s="8">
+        <v>720</v>
+      </c>
+      <c r="I54" s="9">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J54" s="9">
+        <f t="shared" si="1"/>
+        <v>450</v>
+      </c>
+      <c r="K54" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="L54" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="M54" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="N54" s="11" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="12">
@@ -3274,7 +3338,9 @@
       <c r="N57" s="11"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="12"/>
+      <c r="A58" s="12">
+        <v>46309</v>
+      </c>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
       <c r="D58" s="8"/>
@@ -3296,7 +3362,9 @@
       <c r="N58" s="11"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="12"/>
+      <c r="A59" s="12">
+        <v>46310</v>
+      </c>
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
@@ -3318,7 +3386,9 @@
       <c r="N59" s="11"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="12"/>
+      <c r="A60" s="12">
+        <v>46311</v>
+      </c>
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
       <c r="D60" s="8"/>
@@ -3340,7 +3410,9 @@
       <c r="N60" s="11"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="12"/>
+      <c r="A61" s="12">
+        <v>46312</v>
+      </c>
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
@@ -4438,21 +4510,6 @@
       <c r="L110" s="10"/>
       <c r="M110" s="10"/>
       <c r="N110" s="11"/>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="F111" s="8"/>
-    </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="F112" s="8"/>
-    </row>
-    <row r="113" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F113" s="8"/>
-    </row>
-    <row r="114" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F114" s="8"/>
-    </row>
-    <row r="115" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F115" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -4469,15 +4526,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K110">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K110" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L110">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L110" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M110">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M110" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12602477.xlsx
+++ b/12602477.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Naman\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sweeti Oli\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7827EE5-8B20-40B5-8F3D-05CF5A9BA7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9780" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -256,12 +255,18 @@
   </si>
   <si>
     <t xml:space="preserve">I was travelling so I was tiring </t>
+  </si>
+  <si>
+    <t>preparing for exams</t>
+  </si>
+  <si>
+    <t>mid term exam of CN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -728,7 +733,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A39"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -919,7 +924,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N110"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3269,49 +3274,93 @@
       <c r="A55" s="12">
         <v>46306</v>
       </c>
-      <c r="B55" s="8"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
-      <c r="G55" s="8"/>
-      <c r="H55" s="8"/>
-      <c r="I55" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="10"/>
-      <c r="L55" s="10"/>
-      <c r="M55" s="10"/>
-      <c r="N55" s="11"/>
+      <c r="B55" s="8">
+        <v>480</v>
+      </c>
+      <c r="C55" s="8">
+        <v>60</v>
+      </c>
+      <c r="D55" s="8">
+        <v>300</v>
+      </c>
+      <c r="E55" s="8">
+        <v>0</v>
+      </c>
+      <c r="F55" s="8">
+        <v>0</v>
+      </c>
+      <c r="G55" s="8">
+        <v>0</v>
+      </c>
+      <c r="H55" s="8">
+        <v>480</v>
+      </c>
+      <c r="I55" s="9">
+        <f t="shared" si="0"/>
+        <v>1320</v>
+      </c>
+      <c r="J55" s="9">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+      <c r="K55" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="L55" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M55" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="N55" s="11" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="12">
         <v>46307</v>
       </c>
-      <c r="B56" s="8"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8"/>
-      <c r="H56" s="8"/>
-      <c r="I56" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="10"/>
-      <c r="L56" s="10"/>
-      <c r="M56" s="10"/>
-      <c r="N56" s="11"/>
+      <c r="B56" s="8">
+        <v>300</v>
+      </c>
+      <c r="C56" s="8">
+        <v>45</v>
+      </c>
+      <c r="D56" s="8">
+        <v>360</v>
+      </c>
+      <c r="E56" s="8">
+        <v>0</v>
+      </c>
+      <c r="F56" s="8">
+        <v>0</v>
+      </c>
+      <c r="G56" s="8">
+        <v>0</v>
+      </c>
+      <c r="H56" s="8">
+        <v>480</v>
+      </c>
+      <c r="I56" s="9">
+        <f t="shared" si="0"/>
+        <v>1185</v>
+      </c>
+      <c r="J56" s="9">
+        <f t="shared" si="1"/>
+        <v>255</v>
+      </c>
+      <c r="K56" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="L56" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M56" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N56" s="11" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="12">
@@ -4526,15 +4575,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K110" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K110">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L110" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L110">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M110" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M110">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12602477.xlsx
+++ b/12602477.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -260,7 +260,10 @@
     <t>preparing for exams</t>
   </si>
   <si>
-    <t>mid term exam of CN</t>
+    <t xml:space="preserve">mid term exam </t>
+  </si>
+  <si>
+    <t>mid term exam</t>
   </si>
 </sst>
 </file>
@@ -3366,73 +3369,139 @@
       <c r="A57" s="12">
         <v>46308</v>
       </c>
-      <c r="B57" s="8"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8"/>
-      <c r="G57" s="8"/>
-      <c r="H57" s="8"/>
-      <c r="I57" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="10"/>
-      <c r="L57" s="10"/>
-      <c r="M57" s="10"/>
-      <c r="N57" s="11"/>
+      <c r="B57" s="8">
+        <v>360</v>
+      </c>
+      <c r="C57" s="8">
+        <v>60</v>
+      </c>
+      <c r="D57" s="8">
+        <v>360</v>
+      </c>
+      <c r="E57" s="8">
+        <v>0</v>
+      </c>
+      <c r="F57" s="8">
+        <v>0</v>
+      </c>
+      <c r="G57" s="8">
+        <v>0</v>
+      </c>
+      <c r="H57" s="8">
+        <v>480</v>
+      </c>
+      <c r="I57" s="9">
+        <f t="shared" si="0"/>
+        <v>1260</v>
+      </c>
+      <c r="J57" s="9">
+        <f t="shared" si="1"/>
+        <v>180</v>
+      </c>
+      <c r="K57" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="L57" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M57" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N57" s="11" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="12">
         <v>46309</v>
       </c>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="8"/>
-      <c r="I58" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="10"/>
-      <c r="L58" s="10"/>
-      <c r="M58" s="10"/>
-      <c r="N58" s="11"/>
+      <c r="B58" s="8">
+        <v>360</v>
+      </c>
+      <c r="C58" s="8">
+        <v>60</v>
+      </c>
+      <c r="D58" s="8">
+        <v>360</v>
+      </c>
+      <c r="E58" s="8">
+        <v>0</v>
+      </c>
+      <c r="F58" s="8">
+        <v>0</v>
+      </c>
+      <c r="G58" s="8">
+        <v>0</v>
+      </c>
+      <c r="H58" s="8">
+        <v>480</v>
+      </c>
+      <c r="I58" s="9">
+        <f t="shared" si="0"/>
+        <v>1260</v>
+      </c>
+      <c r="J58" s="9">
+        <f t="shared" si="1"/>
+        <v>180</v>
+      </c>
+      <c r="K58" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="L58" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M58" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N58" s="11" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="12">
         <v>46310</v>
       </c>
-      <c r="B59" s="8"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
-      <c r="G59" s="8"/>
-      <c r="H59" s="8"/>
-      <c r="I59" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="10"/>
-      <c r="L59" s="10"/>
-      <c r="M59" s="10"/>
-      <c r="N59" s="11"/>
+      <c r="B59" s="8">
+        <v>480</v>
+      </c>
+      <c r="C59" s="8">
+        <v>60</v>
+      </c>
+      <c r="D59" s="8">
+        <v>360</v>
+      </c>
+      <c r="E59" s="8">
+        <v>0</v>
+      </c>
+      <c r="F59" s="8">
+        <v>0</v>
+      </c>
+      <c r="G59" s="8">
+        <v>0</v>
+      </c>
+      <c r="H59" s="8">
+        <v>480</v>
+      </c>
+      <c r="I59" s="9">
+        <f t="shared" si="0"/>
+        <v>1380</v>
+      </c>
+      <c r="J59" s="9">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="K59" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="L59" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M59" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N59" s="11" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="12">

--- a/12602477.xlsx
+++ b/12602477.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -264,6 +264,9 @@
   </si>
   <si>
     <t>mid term exam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no mid term exam </t>
   </si>
 </sst>
 </file>
@@ -3500,56 +3503,100 @@
         <v>57</v>
       </c>
       <c r="N59" s="11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="12">
         <v>46311</v>
       </c>
-      <c r="B60" s="8"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8"/>
-      <c r="G60" s="8"/>
-      <c r="H60" s="8"/>
-      <c r="I60" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="10"/>
-      <c r="L60" s="10"/>
-      <c r="M60" s="10"/>
-      <c r="N60" s="11"/>
+      <c r="B60" s="8">
+        <v>300</v>
+      </c>
+      <c r="C60" s="8">
+        <v>45</v>
+      </c>
+      <c r="D60" s="8">
+        <v>360</v>
+      </c>
+      <c r="E60" s="8">
+        <v>0</v>
+      </c>
+      <c r="F60" s="8">
+        <v>0</v>
+      </c>
+      <c r="G60" s="8">
+        <v>0</v>
+      </c>
+      <c r="H60" s="8">
+        <v>480</v>
+      </c>
+      <c r="I60" s="9">
+        <f t="shared" si="0"/>
+        <v>1185</v>
+      </c>
+      <c r="J60" s="9">
+        <f t="shared" si="1"/>
+        <v>255</v>
+      </c>
+      <c r="K60" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="L60" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M60" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N60" s="11" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="12">
         <v>46312</v>
       </c>
-      <c r="B61" s="8"/>
-      <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8"/>
-      <c r="G61" s="8"/>
-      <c r="H61" s="8"/>
-      <c r="I61" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="10"/>
-      <c r="L61" s="10"/>
-      <c r="M61" s="10"/>
-      <c r="N61" s="11"/>
+      <c r="B61" s="8">
+        <v>300</v>
+      </c>
+      <c r="C61" s="8">
+        <v>45</v>
+      </c>
+      <c r="D61" s="8">
+        <v>360</v>
+      </c>
+      <c r="E61" s="8">
+        <v>0</v>
+      </c>
+      <c r="F61" s="8">
+        <v>0</v>
+      </c>
+      <c r="G61" s="8">
+        <v>0</v>
+      </c>
+      <c r="H61" s="8">
+        <v>480</v>
+      </c>
+      <c r="I61" s="9">
+        <f t="shared" si="0"/>
+        <v>1185</v>
+      </c>
+      <c r="J61" s="9">
+        <f t="shared" si="1"/>
+        <v>255</v>
+      </c>
+      <c r="K61" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="L61" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M61" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N61" s="11" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="12"/>

--- a/12602477.xlsx
+++ b/12602477.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3599,114 +3599,234 @@
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="12"/>
-      <c r="B62" s="8"/>
-      <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="8"/>
-      <c r="G62" s="8"/>
-      <c r="H62" s="8"/>
-      <c r="I62" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="10"/>
-      <c r="L62" s="10"/>
-      <c r="M62" s="10"/>
-      <c r="N62" s="11"/>
+      <c r="A62" s="12">
+        <v>46313</v>
+      </c>
+      <c r="B62" s="8">
+        <v>480</v>
+      </c>
+      <c r="C62" s="8">
+        <v>45</v>
+      </c>
+      <c r="D62" s="8">
+        <v>0</v>
+      </c>
+      <c r="E62" s="8">
+        <v>0</v>
+      </c>
+      <c r="F62" s="8">
+        <v>0</v>
+      </c>
+      <c r="G62" s="8">
+        <v>0</v>
+      </c>
+      <c r="H62" s="8">
+        <v>480</v>
+      </c>
+      <c r="I62" s="9">
+        <f t="shared" si="0"/>
+        <v>1005</v>
+      </c>
+      <c r="J62" s="9">
+        <f t="shared" si="1"/>
+        <v>435</v>
+      </c>
+      <c r="K62" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="L62" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M62" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N62" s="11" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="12"/>
-      <c r="B63" s="8"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="8"/>
-      <c r="G63" s="8"/>
-      <c r="H63" s="8"/>
-      <c r="I63" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="10"/>
-      <c r="L63" s="10"/>
-      <c r="M63" s="10"/>
-      <c r="N63" s="11"/>
+      <c r="A63" s="12">
+        <v>46314</v>
+      </c>
+      <c r="B63" s="8">
+        <v>480</v>
+      </c>
+      <c r="C63" s="8">
+        <v>60</v>
+      </c>
+      <c r="D63" s="8">
+        <v>60</v>
+      </c>
+      <c r="E63" s="8">
+        <v>60</v>
+      </c>
+      <c r="F63" s="8">
+        <v>0</v>
+      </c>
+      <c r="G63" s="8">
+        <v>0</v>
+      </c>
+      <c r="H63" s="8">
+        <v>480</v>
+      </c>
+      <c r="I63" s="9">
+        <f t="shared" si="0"/>
+        <v>1140</v>
+      </c>
+      <c r="J63" s="9">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+      <c r="K63" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="L63" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M63" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N63" s="11" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="12"/>
-      <c r="B64" s="8"/>
-      <c r="C64" s="8"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="8"/>
-      <c r="G64" s="8"/>
-      <c r="H64" s="8"/>
-      <c r="I64" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="10"/>
-      <c r="L64" s="10"/>
-      <c r="M64" s="10"/>
-      <c r="N64" s="11"/>
+      <c r="A64" s="12">
+        <v>46315</v>
+      </c>
+      <c r="B64" s="8">
+        <v>480</v>
+      </c>
+      <c r="C64" s="8">
+        <v>60</v>
+      </c>
+      <c r="D64" s="8">
+        <v>60</v>
+      </c>
+      <c r="E64" s="8">
+        <v>60</v>
+      </c>
+      <c r="F64" s="8">
+        <v>0</v>
+      </c>
+      <c r="G64" s="8">
+        <v>0</v>
+      </c>
+      <c r="H64" s="8">
+        <v>480</v>
+      </c>
+      <c r="I64" s="9">
+        <f t="shared" si="0"/>
+        <v>1140</v>
+      </c>
+      <c r="J64" s="9">
+        <f t="shared" si="1"/>
+        <v>300</v>
+      </c>
+      <c r="K64" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="L64" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M64" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N64" s="11" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="12"/>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8"/>
-      <c r="G65" s="8"/>
-      <c r="H65" s="8"/>
-      <c r="I65" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="10"/>
-      <c r="L65" s="10"/>
-      <c r="M65" s="10"/>
-      <c r="N65" s="11"/>
+      <c r="A65" s="12">
+        <v>46316</v>
+      </c>
+      <c r="B65" s="8">
+        <v>300</v>
+      </c>
+      <c r="C65" s="8">
+        <v>60</v>
+      </c>
+      <c r="D65" s="8">
+        <v>120</v>
+      </c>
+      <c r="E65" s="8">
+        <v>120</v>
+      </c>
+      <c r="F65" s="8">
+        <v>200</v>
+      </c>
+      <c r="G65" s="8">
+        <v>4</v>
+      </c>
+      <c r="H65" s="8">
+        <v>360</v>
+      </c>
+      <c r="I65" s="9">
+        <f t="shared" si="0"/>
+        <v>1160</v>
+      </c>
+      <c r="J65" s="9">
+        <f t="shared" si="1"/>
+        <v>280</v>
+      </c>
+      <c r="K65" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="L65" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="M65" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N65" s="11" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="12"/>
-      <c r="B66" s="8"/>
-      <c r="C66" s="8"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
-      <c r="G66" s="8"/>
-      <c r="H66" s="8"/>
-      <c r="I66" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="10"/>
-      <c r="L66" s="10"/>
-      <c r="M66" s="10"/>
-      <c r="N66" s="11"/>
+      <c r="A66" s="12">
+        <v>46317</v>
+      </c>
+      <c r="B66" s="8">
+        <v>300</v>
+      </c>
+      <c r="C66" s="8">
+        <v>60</v>
+      </c>
+      <c r="D66" s="8">
+        <v>60</v>
+      </c>
+      <c r="E66" s="8">
+        <v>120</v>
+      </c>
+      <c r="F66" s="8">
+        <v>350</v>
+      </c>
+      <c r="G66" s="8">
+        <v>7</v>
+      </c>
+      <c r="H66" s="8">
+        <v>300</v>
+      </c>
+      <c r="I66" s="9">
+        <f t="shared" si="0"/>
+        <v>1190</v>
+      </c>
+      <c r="J66" s="9">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="K66" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="L66" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="M66" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="N66" s="11" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="12"/>

--- a/12602477.xlsx
+++ b/12602477.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3829,73 +3829,147 @@
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="12"/>
-      <c r="B67" s="8"/>
-      <c r="C67" s="8"/>
-      <c r="D67" s="8"/>
-      <c r="E67" s="8"/>
-      <c r="F67" s="8"/>
-      <c r="G67" s="8"/>
-      <c r="H67" s="8"/>
-      <c r="I67" s="9" t="str">
+      <c r="A67" s="12">
+        <v>46318</v>
+      </c>
+      <c r="B67" s="8">
+        <v>300</v>
+      </c>
+      <c r="C67" s="8">
+        <v>60</v>
+      </c>
+      <c r="D67" s="8">
+        <v>60</v>
+      </c>
+      <c r="E67" s="8">
+        <v>60</v>
+      </c>
+      <c r="F67" s="8">
+        <v>300</v>
+      </c>
+      <c r="G67" s="8">
+        <v>6</v>
+      </c>
+      <c r="H67" s="8">
+        <v>300</v>
+      </c>
+      <c r="I67" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="9" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J67" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="10"/>
-      <c r="L67" s="10"/>
-      <c r="M67" s="10"/>
-      <c r="N67" s="11"/>
+        <v>360</v>
+      </c>
+      <c r="K67" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="L67" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="M67" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="N67" s="11" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="12"/>
-      <c r="B68" s="8"/>
-      <c r="C68" s="8"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
-      <c r="G68" s="8"/>
-      <c r="H68" s="8"/>
-      <c r="I68" s="9" t="str">
+      <c r="A68" s="12">
+        <v>46319</v>
+      </c>
+      <c r="B68" s="8">
+        <v>480</v>
+      </c>
+      <c r="C68" s="8">
+        <v>45</v>
+      </c>
+      <c r="D68" s="8">
+        <v>60</v>
+      </c>
+      <c r="E68" s="8">
+        <v>60</v>
+      </c>
+      <c r="F68" s="8">
+        <v>0</v>
+      </c>
+      <c r="G68" s="8">
+        <v>0</v>
+      </c>
+      <c r="H68" s="8">
+        <v>480</v>
+      </c>
+      <c r="I68" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="9" t="str">
+        <v>1125</v>
+      </c>
+      <c r="J68" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="10"/>
-      <c r="L68" s="10"/>
-      <c r="M68" s="10"/>
-      <c r="N68" s="11"/>
+        <v>315</v>
+      </c>
+      <c r="K68" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="L68" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M68" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N68" s="11" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="12"/>
-      <c r="B69" s="8"/>
-      <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="8"/>
-      <c r="G69" s="8"/>
-      <c r="H69" s="8"/>
-      <c r="I69" s="9" t="str">
+      <c r="A69" s="12">
+        <v>46320</v>
+      </c>
+      <c r="B69" s="8">
+        <v>480</v>
+      </c>
+      <c r="C69" s="8">
+        <v>45</v>
+      </c>
+      <c r="D69" s="8">
+        <v>120</v>
+      </c>
+      <c r="E69" s="8">
+        <v>60</v>
+      </c>
+      <c r="F69" s="8">
+        <v>0</v>
+      </c>
+      <c r="G69" s="8">
+        <v>0</v>
+      </c>
+      <c r="H69" s="8">
+        <v>480</v>
+      </c>
+      <c r="I69" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="9" t="str">
+        <v>1185</v>
+      </c>
+      <c r="J69" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="10"/>
-      <c r="L69" s="10"/>
-      <c r="M69" s="10"/>
-      <c r="N69" s="11"/>
+        <v>255</v>
+      </c>
+      <c r="K69" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="L69" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M69" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N69" s="11" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="12"/>
+      <c r="A70" s="12">
+        <v>46321</v>
+      </c>
       <c r="B70" s="8"/>
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
@@ -3917,7 +3991,9 @@
       <c r="N70" s="11"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="12"/>
+      <c r="A71" s="12">
+        <v>46322</v>
+      </c>
       <c r="B71" s="8"/>
       <c r="C71" s="8"/>
       <c r="D71" s="8"/>
@@ -3939,7 +4015,9 @@
       <c r="N71" s="11"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="12"/>
+      <c r="A72" s="12">
+        <v>46323</v>
+      </c>
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
       <c r="D72" s="8"/>

--- a/12602477.xlsx
+++ b/12602477.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -267,6 +267,9 @@
   </si>
   <si>
     <t xml:space="preserve">no mid term exam </t>
+  </si>
+  <si>
+    <t>it was a tiring day</t>
   </si>
 </sst>
 </file>
@@ -3970,49 +3973,93 @@
       <c r="A70" s="12">
         <v>46321</v>
       </c>
-      <c r="B70" s="8"/>
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8"/>
-      <c r="G70" s="8"/>
-      <c r="H70" s="8"/>
-      <c r="I70" s="9" t="str">
+      <c r="B70" s="8">
+        <v>480</v>
+      </c>
+      <c r="C70" s="8">
+        <v>60</v>
+      </c>
+      <c r="D70" s="8">
+        <v>120</v>
+      </c>
+      <c r="E70" s="8">
+        <v>60</v>
+      </c>
+      <c r="F70" s="8">
+        <v>0</v>
+      </c>
+      <c r="G70" s="8">
+        <v>0</v>
+      </c>
+      <c r="H70" s="8">
+        <v>480</v>
+      </c>
+      <c r="I70" s="9">
         <f t="shared" ref="I70:I110" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="9" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J70" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K70" s="10"/>
-      <c r="L70" s="10"/>
-      <c r="M70" s="10"/>
-      <c r="N70" s="11"/>
+        <v>240</v>
+      </c>
+      <c r="K70" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="L70" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M70" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N70" s="11" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="12">
         <v>46322</v>
       </c>
-      <c r="B71" s="8"/>
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-      <c r="G71" s="8"/>
-      <c r="H71" s="8"/>
-      <c r="I71" s="9" t="str">
+      <c r="B71" s="8">
+        <v>360</v>
+      </c>
+      <c r="C71" s="8">
+        <v>60</v>
+      </c>
+      <c r="D71" s="8">
+        <v>120</v>
+      </c>
+      <c r="E71" s="8">
+        <v>60</v>
+      </c>
+      <c r="F71" s="8">
+        <v>350</v>
+      </c>
+      <c r="G71" s="8">
+        <v>7</v>
+      </c>
+      <c r="H71" s="8">
+        <v>480</v>
+      </c>
+      <c r="I71" s="9">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="9" t="str">
+        <v>1430</v>
+      </c>
+      <c r="J71" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K71" s="10"/>
-      <c r="L71" s="10"/>
-      <c r="M71" s="10"/>
-      <c r="N71" s="11"/>
+        <v>10</v>
+      </c>
+      <c r="K71" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="L71" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="M71" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="N71" s="11" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="12">
